--- a/jira_export_2026-07-01.xlsx
+++ b/jira_export_2026-07-01.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>78,427 €</t>
+          <t>79,036 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>87.1%</t>
+          <t>87.8%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -772,14 +772,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>29,800 €</t>
+          <t>29,966 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>48,627 €</t>
+          <t>49,070 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -912,7 +912,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>255</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -1466,8 +1466,8 @@
       <c r="N10" s="16" t="n">
         <v>353.5</v>
       </c>
-      <c r="O10" s="17" t="n">
-        <v>0</v>
+      <c r="O10" s="16" t="n">
+        <v>353.5</v>
       </c>
       <c r="P10" s="16" t="n">
         <v>0</v>
@@ -6507,10 +6507,10 @@
         <v>0</v>
       </c>
       <c r="O81" s="13" t="n">
-        <v>0</v>
+        <v>109.973</v>
       </c>
       <c r="P81" s="13" t="n">
-        <v>0</v>
+        <v>20.95</v>
       </c>
     </row>
     <row r="82">
@@ -6859,7 +6859,7 @@
         <v>360</v>
       </c>
       <c r="O86" s="17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P86" s="16" t="n">
         <v>0</v>
@@ -7363,10 +7363,10 @@
         <v>472.005</v>
       </c>
       <c r="O93" s="17" t="n">
-        <v>0</v>
+        <v>55.53</v>
       </c>
       <c r="P93" s="13" t="n">
-        <v>0</v>
+        <v>7.93</v>
       </c>
     </row>
     <row r="94">
@@ -14669,10 +14669,10 @@
         <v>57265.59</v>
       </c>
       <c r="O205" s="19" t="n">
-        <v>78426.94100000001</v>
+        <v>79035.944</v>
       </c>
       <c r="P205" s="19" t="n">
-        <v>151.55</v>
+        <v>152.73</v>
       </c>
     </row>
   </sheetData>
@@ -16205,10 +16205,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>385077</v>
+        <v>384468</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>181433</v>
+        <v>180824</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>203645</v>
@@ -16230,10 +16230,10 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>189634</v>
+        <v>189469</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>85130</v>
+        <v>84964</v>
       </c>
       <c r="D6" s="26" t="n">
         <v>104505</v>
@@ -16255,10 +16255,10 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>195443</v>
+        <v>195000</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>96303</v>
+        <v>95859</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>99140</v>

--- a/jira_export_2026-07-01.xlsx
+++ b/jira_export_2026-07-01.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>79,036 €</t>
+          <t>80,583 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>87.8%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -772,14 +772,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>29,966 €</t>
+          <t>31,140 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>49,070 €</t>
+          <t>49,444 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -1891,10 +1891,10 @@
         <v>0</v>
       </c>
       <c r="O16" s="16" t="n">
-        <v>170</v>
+        <v>340</v>
       </c>
       <c r="P16" s="16" t="n">
-        <v>136</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17">
@@ -2323,10 +2323,10 @@
         <v>0</v>
       </c>
       <c r="O22" s="16" t="n">
-        <v>1312.5</v>
+        <v>1837.5</v>
       </c>
       <c r="P22" s="16" t="n">
-        <v>1050</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="23">
@@ -2467,10 +2467,10 @@
         <v>0</v>
       </c>
       <c r="O24" s="16" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="P24" s="16" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25">
@@ -2747,10 +2747,10 @@
         <v>0</v>
       </c>
       <c r="O28" s="16" t="n">
-        <v>0</v>
+        <v>460</v>
       </c>
       <c r="P28" s="16" t="n">
-        <v>0</v>
+        <v>306.67</v>
       </c>
     </row>
     <row r="29">
@@ -3739,10 +3739,10 @@
         <v>203.5</v>
       </c>
       <c r="O42" s="16" t="n">
-        <v>203.5</v>
+        <v>407</v>
       </c>
       <c r="P42" s="16" t="n">
-        <v>116.29</v>
+        <v>232.57</v>
       </c>
     </row>
     <row r="43">
@@ -14669,10 +14669,10 @@
         <v>57265.59</v>
       </c>
       <c r="O205" s="19" t="n">
-        <v>79035.944</v>
+        <v>80583.444</v>
       </c>
       <c r="P205" s="19" t="n">
-        <v>152.73</v>
+        <v>155.72</v>
       </c>
     </row>
   </sheetData>
@@ -16205,16 +16205,16 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>384468</v>
+        <v>395307</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>180824</v>
+        <v>191866</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>203645</v>
+        <v>203441</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>172285</v>
+        <v>172082</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>15760</v>
@@ -16230,10 +16230,10 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>189469</v>
+        <v>188295</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>84964</v>
+        <v>83790</v>
       </c>
       <c r="D6" s="26" t="n">
         <v>104505</v>
@@ -16255,16 +16255,16 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>195000</v>
+        <v>207012</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>95859</v>
+        <v>108075</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>99140</v>
+        <v>98937</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>75289</v>
+        <v>75086</v>
       </c>
       <c r="F7" s="27" t="n">
         <v>12700</v>
@@ -16284,7 +16284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -16308,7 +16308,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 37 commande(s)</t>
+          <t>Épics créées ce mois — 38 commande(s)</t>
         </is>
       </c>
     </row>
@@ -16363,22 +16363,22 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34345</t>
+          <t>PDMDEP-34380</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34337</t>
+          <t>PDMDEP-34287</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>Commune de Chalons-sur-Saone</t>
+          <t>COMMUNE DE LUNEL</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -16388,19 +16388,11 @@
       </c>
       <c r="F5" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
-      <c r="G5" s="15" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
-      <c r="H5" s="15" t="inlineStr">
-        <is>
-          <t>00171711</t>
-        </is>
-      </c>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr"/>
+      <c r="H5" s="15" t="inlineStr"/>
       <c r="I5" s="26" t="n">
         <v>0</v>
       </c>
@@ -17038,22 +17030,22 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34326</t>
+          <t>PDMDEP-34117</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34319</t>
+          <t>PDMDEP-34108</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Commune de Mouscron (BE)</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
@@ -17073,22 +17065,22 @@
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>00171691</t>
+          <t>00170907</t>
         </is>
       </c>
       <c r="I20" s="27" t="n">
-        <v>0</v>
+        <v>3535</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34310</t>
+          <t>PDMDEP-34345</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34303</t>
+          <t>PDMDEP-34337</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
@@ -17098,7 +17090,7 @@
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAP</t>
+          <t>Commune de Chalons-sur-Saone</t>
         </is>
       </c>
       <c r="E21" s="15" t="inlineStr">
@@ -17108,7 +17100,7 @@
       </c>
       <c r="F21" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
@@ -17118,7 +17110,7 @@
       </c>
       <c r="H21" s="15" t="inlineStr">
         <is>
-          <t>00171605</t>
+          <t>00171711</t>
         </is>
       </c>
       <c r="I21" s="26" t="n">
@@ -17128,22 +17120,22 @@
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34258</t>
+          <t>PDMDEP-34155</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34147</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>Mairie de Vaison la romaine</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
@@ -17153,7 +17145,7 @@
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
@@ -17163,32 +17155,32 @@
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>00171361</t>
+          <t>00171080</t>
         </is>
       </c>
       <c r="I22" s="27" t="n">
-        <v>0</v>
+        <v>1414.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34227</t>
+          <t>PDMDEP-34326</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34319</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t>Commune de Mouscron (BE)</t>
         </is>
       </c>
       <c r="E23" s="15" t="inlineStr">
@@ -17201,35 +17193,39 @@
           <t>Migration</t>
         </is>
       </c>
-      <c r="G23" s="15" t="inlineStr"/>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
       <c r="H23" s="15" t="inlineStr">
         <is>
-          <t>2026-0210095</t>
+          <t>00171691</t>
         </is>
       </c>
       <c r="I23" s="26" t="n">
-        <v>32077</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34310</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34303</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNE DE GAP</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
@@ -17239,7 +17235,7 @@
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
@@ -17249,22 +17245,22 @@
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00171605</t>
         </is>
       </c>
       <c r="I24" s="27" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34201</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
@@ -17274,7 +17270,7 @@
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
@@ -17284,7 +17280,7 @@
       </c>
       <c r="F25" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="G25" s="15" t="inlineStr">
@@ -17294,7 +17290,7 @@
       </c>
       <c r="H25" s="15" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171162</t>
         </is>
       </c>
       <c r="I25" s="26" t="n">
@@ -17304,22 +17300,22 @@
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34155</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34147</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Mairie de Vaison la romaine</t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
@@ -17329,7 +17325,7 @@
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G26" s="12" t="inlineStr">
@@ -17339,32 +17335,32 @@
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>00171080</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="I26" s="27" t="n">
-        <v>1414.5</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34117</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34108</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
@@ -17384,32 +17380,32 @@
       </c>
       <c r="H27" s="15" t="inlineStr">
         <is>
-          <t>00170907</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="I27" s="26" t="n">
-        <v>3535</v>
+        <v>10636</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
@@ -17419,7 +17415,7 @@
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G28" s="12" t="inlineStr">
@@ -17429,73 +17425,73 @@
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="I28" s="27" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33833</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33822</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="F29" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G29" s="15" t="inlineStr"/>
       <c r="H29" s="15" t="inlineStr">
         <is>
-          <t>00169872</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="I29" s="26" t="n">
-        <v>2625</v>
+        <v>32077</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
@@ -17515,32 +17511,32 @@
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="I30" s="27" t="n">
-        <v>1095.5</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33703</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33699</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
         </is>
       </c>
       <c r="E31" s="15" t="inlineStr">
@@ -17560,32 +17556,32 @@
       </c>
       <c r="H31" s="15" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169363</t>
         </is>
       </c>
       <c r="I31" s="26" t="n">
-        <v>1890</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33794</t>
+          <t>PDMDEP-33724</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33790</t>
+          <t>PDMDEP-33720</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
@@ -17605,32 +17601,32 @@
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>00169697</t>
+          <t>00169462</t>
         </is>
       </c>
       <c r="I32" s="27" t="n">
-        <v>6655</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E33" s="15" t="inlineStr">
@@ -17650,22 +17646,22 @@
       </c>
       <c r="H33" s="15" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="I33" s="26" t="n">
-        <v>2300</v>
+        <v>6655</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33733</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33729</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
@@ -17675,7 +17671,7 @@
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
@@ -17695,32 +17691,32 @@
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>00169480</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="I34" s="27" t="n">
-        <v>755</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33724</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33720</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E35" s="15" t="inlineStr">
@@ -17740,32 +17736,32 @@
       </c>
       <c r="H35" s="15" t="inlineStr">
         <is>
-          <t>00169462</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="I35" s="26" t="n">
-        <v>1000</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33703</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33699</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
@@ -17785,32 +17781,32 @@
       </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>00169363</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="I36" s="27" t="n">
-        <v>1350</v>
+        <v>1095.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33570</t>
+          <t>PDMDEP-33833</t>
         </is>
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33566</t>
+          <t>PDMDEP-33822</t>
         </is>
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="D37" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LILLE</t>
+          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
         </is>
       </c>
       <c r="E37" s="15" t="inlineStr">
@@ -17823,39 +17819,35 @@
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G37" s="15" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
+      <c r="G37" s="15" t="inlineStr"/>
       <c r="H37" s="15" t="inlineStr">
         <is>
-          <t>00168466</t>
+          <t>00169872</t>
         </is>
       </c>
       <c r="I37" s="26" t="n">
-        <v>895</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
@@ -17875,32 +17867,32 @@
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="I38" s="27" t="n">
-        <v>7200</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-33570</t>
         </is>
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-33566</t>
         </is>
       </c>
       <c r="C39" s="15" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="D39" s="15" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>COMMUNE DE LILLE</t>
         </is>
       </c>
       <c r="E39" s="15" t="inlineStr">
@@ -17920,11 +17912,11 @@
       </c>
       <c r="H39" s="15" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00168466</t>
         </is>
       </c>
       <c r="I39" s="26" t="n">
-        <v>12429</v>
+        <v>895</v>
       </c>
     </row>
     <row r="40">
@@ -17975,73 +17967,97 @@
     <row r="41">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33733</t>
         </is>
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33729</t>
         </is>
       </c>
       <c r="C41" s="15" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
+        </is>
+      </c>
+      <c r="E41" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F41" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G41" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H41" s="15" t="inlineStr">
+        <is>
+          <t>00169480</t>
+        </is>
+      </c>
+      <c r="I41" s="26" t="n">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33955</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33949</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="D41" s="15" t="inlineStr">
-        <is>
-          <t>Commune de Thionville</t>
-        </is>
-      </c>
-      <c r="E41" s="15" t="inlineStr">
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>Commune de Colmar</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F41" s="15" t="inlineStr">
+      <c r="F42" s="12" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G41" s="15" t="inlineStr">
+      <c r="G42" s="12" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H41" s="15" t="inlineStr">
-        <is>
-          <t>00170299</t>
-        </is>
-      </c>
-      <c r="I41" s="26" t="n">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="18" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B42" s="18" t="n"/>
-      <c r="C42" s="18" t="n"/>
-      <c r="D42" s="18" t="n"/>
-      <c r="E42" s="18" t="n"/>
-      <c r="F42" s="18" t="n"/>
-      <c r="G42" s="18" t="n"/>
-      <c r="H42" s="18" t="inlineStr">
-        <is>
-          <t>37 commande(s)</t>
-        </is>
-      </c>
-      <c r="I42" s="25" t="n">
-        <v>118111</v>
+      <c r="H42" s="12" t="inlineStr">
+        <is>
+          <t>00170302</t>
+        </is>
+      </c>
+      <c r="I42" s="27" t="n">
+        <v>12429</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="18" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B43" s="18" t="n"/>
@@ -18052,17 +18068,17 @@
       <c r="G43" s="18" t="n"/>
       <c r="H43" s="18" t="inlineStr">
         <is>
-          <t>13 commande(s)</t>
+          <t>38 commande(s)</t>
         </is>
       </c>
       <c r="I43" s="25" t="n">
-        <v>42234</v>
+        <v>130497</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="18" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B44" s="18" t="n"/>
@@ -18073,11 +18089,32 @@
       <c r="G44" s="18" t="n"/>
       <c r="H44" s="18" t="inlineStr">
         <is>
-          <t>24 commande(s)</t>
+          <t>13 commande(s)</t>
         </is>
       </c>
       <c r="I44" s="25" t="n">
-        <v>75876</v>
+        <v>42234</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="18" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B45" s="18" t="n"/>
+      <c r="C45" s="18" t="n"/>
+      <c r="D45" s="18" t="n"/>
+      <c r="E45" s="18" t="n"/>
+      <c r="F45" s="18" t="n"/>
+      <c r="G45" s="18" t="n"/>
+      <c r="H45" s="18" t="inlineStr">
+        <is>
+          <t>25 commande(s)</t>
+        </is>
+      </c>
+      <c r="I45" s="25" t="n">
+        <v>88262</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-07-01.xlsx
+++ b/jira_export_2026-07-01.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>80,583 €</t>
+          <t>81,371 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -772,14 +772,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>31,140 €</t>
+          <t>31,324 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>49,444 €</t>
+          <t>50,047 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -4795,10 +4795,10 @@
         <v>184.5</v>
       </c>
       <c r="O57" s="13" t="n">
-        <v>332.1</v>
+        <v>516.6</v>
       </c>
       <c r="P57" s="13" t="n">
-        <v>1328.4</v>
+        <v>2066.4</v>
       </c>
     </row>
     <row r="58">
@@ -4939,7 +4939,7 @@
         <v>603.5</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>603.5</v>
+        <v>1207</v>
       </c>
       <c r="P59" s="13" t="n">
         <v>0</v>
@@ -14669,10 +14669,10 @@
         <v>57265.59</v>
       </c>
       <c r="O205" s="19" t="n">
-        <v>80583.444</v>
+        <v>81371.444</v>
       </c>
       <c r="P205" s="19" t="n">
-        <v>155.72</v>
+        <v>157.24</v>
       </c>
     </row>
   </sheetData>
@@ -16205,16 +16205,16 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>395307</v>
+        <v>394519</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>191866</v>
+        <v>191681</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>203441</v>
+        <v>202838</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>172082</v>
+        <v>171478</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>15760</v>
@@ -16230,10 +16230,10 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>188295</v>
+        <v>188110</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>83790</v>
+        <v>83606</v>
       </c>
       <c r="D6" s="26" t="n">
         <v>104505</v>
@@ -16255,16 +16255,16 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>207012</v>
+        <v>206409</v>
       </c>
       <c r="C7" s="27" t="n">
         <v>108075</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>98937</v>
+        <v>98333</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>75086</v>
+        <v>74482</v>
       </c>
       <c r="F7" s="27" t="n">
         <v>12700</v>

--- a/jira_export_2026-07-01.xlsx
+++ b/jira_export_2026-07-01.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>-434 €</t>
+          <t>219 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -760,14 +760,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>0 €</t>
+          <t>219 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>-434 €</t>
+          <t>0 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>2 h</t>
+          <t>9 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>254</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P72"/>
+  <dimension ref="A1:P74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1317,7 +1317,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L8" s="15" t="inlineStr">
         <is>
@@ -1333,10 +1333,10 @@
         <v>657.3</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>0</v>
+        <v>219.1</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>0</v>
+        <v>175.28</v>
       </c>
     </row>
     <row r="9">
@@ -2037,7 +2037,7 @@
         <v>2</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L18" s="15" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>5</v>
       </c>
       <c r="K44" s="15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L44" s="15" t="inlineStr">
         <is>
@@ -4510,32 +4510,32 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29480</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D'EYSINES - Migration V2</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D'EYSINES</t>
+          <t>MAIRE DE PONTARLIER</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
@@ -4545,35 +4545,35 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29485</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00145493</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>-133</v>
+        <v>0</v>
       </c>
       <c r="O53" s="12" t="n">
-        <v>-434</v>
+        <v>0</v>
       </c>
       <c r="P53" s="12" t="n">
         <v>0</v>
@@ -5290,22 +5290,22 @@
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21546</t>
+          <t>PDMDEP-22996</t>
         </is>
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>VILLEURBANNE</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E64" s="15" t="n">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="F64" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G64" s="15" t="inlineStr">
@@ -5328,29 +5328,29 @@
       </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
-          <t>05/05/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="J64" s="15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K64" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L64" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28038</t>
+          <t>PDMDEP-28051</t>
         </is>
       </c>
       <c r="M64" s="15" t="inlineStr">
         <is>
-          <t>478867</t>
+          <t>487190</t>
         </is>
       </c>
       <c r="N64" s="16" t="n">
-        <v>1413.6</v>
-      </c>
-      <c r="O64" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P64" s="16" t="n">
@@ -5360,22 +5360,22 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21546</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>VILLEURBANNE</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
@@ -5398,27 +5398,27 @@
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K65" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28038</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>478867</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>250</v>
+        <v>1413.6</v>
       </c>
       <c r="O65" s="13" t="n">
         <v>0</v>
@@ -5430,22 +5430,22 @@
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E66" s="15" t="n">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="I66" s="15" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J66" s="15" t="n">
@@ -5479,16 +5479,16 @@
       </c>
       <c r="L66" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M66" s="15" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N66" s="16" t="n">
-        <v>460</v>
+        <v>250</v>
       </c>
       <c r="O66" s="13" t="n">
         <v>0</v>
@@ -5500,12 +5500,12 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-19385</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARCUEIL</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
@@ -5533,34 +5533,34 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>24/02/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27535</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>465345</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O67" s="12" t="n">
+        <v>460</v>
+      </c>
+      <c r="O67" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P67" s="12" t="n">
@@ -5570,22 +5570,22 @@
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-19385</t>
         </is>
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>COMMUNE D'ARCUEIL</t>
         </is>
       </c>
       <c r="E68" s="15" t="n">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="F68" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G68" s="15" t="inlineStr">
@@ -5603,34 +5603,34 @@
       </c>
       <c r="H68" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I68" s="15" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>24/02/2025</t>
         </is>
       </c>
       <c r="J68" s="15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K68" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L68" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-27535</t>
         </is>
       </c>
       <c r="M68" s="15" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>465345</t>
         </is>
       </c>
       <c r="N68" s="16" t="n">
-        <v>240</v>
-      </c>
-      <c r="O68" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P68" s="16" t="n">
@@ -5640,22 +5640,22 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
@@ -5673,34 +5673,34 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
         <v>19</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28020</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="O69" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P69" s="12" t="n">
@@ -5710,21 +5710,27 @@
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="C70" s="15" t="inlineStr"/>
+          <t>[CD 38] Reprise de 1644 AP</t>
+        </is>
+      </c>
+      <c r="C70" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="E70" s="15" t="inlineStr"/>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+        </is>
+      </c>
+      <c r="E70" s="15" t="n">
+        <v/>
+      </c>
       <c r="F70" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -5735,32 +5741,36 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H70" s="15" t="inlineStr"/>
+      <c r="H70" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I70" s="15" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J70" s="15" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="K70" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L70" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33362</t>
+          <t>PDMDEP-28020</t>
         </is>
       </c>
       <c r="M70" s="15" t="inlineStr">
         <is>
-          <t>00167140</t>
+          <t>458057</t>
         </is>
       </c>
       <c r="N70" s="16" t="n">
-        <v>510.6</v>
-      </c>
-      <c r="O70" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P70" s="16" t="n">
@@ -5770,89 +5780,211 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
+          <t>PDMDEP-16868</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>[Limoges] migration placier</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>Limoges</t>
+        </is>
+      </c>
+      <c r="E71" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F71" s="11" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="G71" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H71" s="11" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="I71" s="11" t="inlineStr">
+        <is>
+          <t>26/09/2024</t>
+        </is>
+      </c>
+      <c r="J71" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="K71" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L71" s="11" t="inlineStr"/>
+      <c r="M71" s="11" t="inlineStr"/>
+      <c r="N71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="14" t="inlineStr">
+        <is>
+          <t>PSC-1270</t>
+        </is>
+      </c>
+      <c r="B72" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="C72" s="15" t="inlineStr"/>
+      <c r="D72" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="E72" s="15" t="inlineStr"/>
+      <c r="F72" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G72" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H72" s="15" t="inlineStr"/>
+      <c r="I72" s="15" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J72" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K72" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M72" s="15" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N72" s="16" t="n">
+        <v>510.6</v>
+      </c>
+      <c r="O72" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
           <t>PSC-1228</t>
         </is>
       </c>
-      <c r="B71" s="11" t="inlineStr">
+      <c r="B73" s="11" t="inlineStr">
         <is>
           <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
-      <c r="C71" s="11" t="inlineStr"/>
-      <c r="D71" s="11" t="inlineStr">
+      <c r="C73" s="11" t="inlineStr"/>
+      <c r="D73" s="11" t="inlineStr">
         <is>
           <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
-      <c r="E71" s="11" t="inlineStr"/>
-      <c r="F71" s="11" t="inlineStr">
+      <c r="E73" s="11" t="inlineStr"/>
+      <c r="F73" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G71" s="11" t="inlineStr">
+      <c r="G73" s="11" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H71" s="11" t="inlineStr"/>
-      <c r="I71" s="11" t="inlineStr">
+      <c r="H73" s="11" t="inlineStr"/>
+      <c r="I73" s="11" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="J71" s="11" t="n">
+      <c r="J73" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="K71" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="11" t="inlineStr">
+      <c r="K73" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-32829</t>
         </is>
       </c>
-      <c r="M71" s="11" t="inlineStr">
+      <c r="M73" s="11" t="inlineStr">
         <is>
           <t>00163534</t>
         </is>
       </c>
-      <c r="N71" s="12" t="n">
+      <c r="N73" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="O71" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="17" t="inlineStr">
+      <c r="O73" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B72" s="17" t="inlineStr"/>
-      <c r="C72" s="17" t="inlineStr"/>
-      <c r="D72" s="17" t="inlineStr"/>
-      <c r="E72" s="17" t="inlineStr"/>
-      <c r="F72" s="17" t="inlineStr"/>
-      <c r="G72" s="17" t="inlineStr"/>
-      <c r="H72" s="17" t="inlineStr"/>
-      <c r="I72" s="17" t="inlineStr"/>
-      <c r="J72" s="17" t="inlineStr"/>
-      <c r="K72" s="17" t="inlineStr"/>
-      <c r="L72" s="17" t="inlineStr"/>
-      <c r="M72" s="17" t="inlineStr"/>
-      <c r="N72" s="18" t="n">
-        <v>56618.68</v>
-      </c>
-      <c r="O72" s="18" t="n">
-        <v>-434</v>
-      </c>
-      <c r="P72" s="18" t="n">
-        <v>-578.67</v>
+      <c r="B74" s="17" t="inlineStr"/>
+      <c r="C74" s="17" t="inlineStr"/>
+      <c r="D74" s="17" t="inlineStr"/>
+      <c r="E74" s="17" t="inlineStr"/>
+      <c r="F74" s="17" t="inlineStr"/>
+      <c r="G74" s="17" t="inlineStr"/>
+      <c r="H74" s="17" t="inlineStr"/>
+      <c r="I74" s="17" t="inlineStr"/>
+      <c r="J74" s="17" t="inlineStr"/>
+      <c r="K74" s="17" t="inlineStr"/>
+      <c r="L74" s="17" t="inlineStr"/>
+      <c r="M74" s="17" t="inlineStr"/>
+      <c r="N74" s="18" t="n">
+        <v>56751.68</v>
+      </c>
+      <c r="O74" s="18" t="n">
+        <v>219.1</v>
+      </c>
+      <c r="P74" s="18" t="n">
+        <v>30.22</v>
       </c>
     </row>
   </sheetData>
@@ -5925,6 +6057,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId69"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6499,7 +6633,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>0.75</v>
+        <v>6.75</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>0</v>
@@ -6508,7 +6642,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>0.75</v>
+        <v>6.75</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>0</v>
@@ -6518,7 +6652,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1.4%</t>
         </is>
       </c>
     </row>
@@ -6532,13 +6666,13 @@
         <v>0</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D6" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>0</v>
@@ -6548,7 +6682,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
     </row>
@@ -6560,7 +6694,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -6645,10 +6779,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>394519</v>
+        <v>394300</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>191681</v>
+        <v>191462</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>202838</v>
@@ -6670,10 +6804,10 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>188110</v>
+        <v>187891</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>83606</v>
+        <v>83387</v>
       </c>
       <c r="D6" s="25" t="n">
         <v>104505</v>

--- a/jira_export_2026-07-01.xlsx
+++ b/jira_export_2026-07-01.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>219 €</t>
+          <t>1,298 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -767,7 +767,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>0 €</t>
+          <t>1,079 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>9 h</t>
+          <t>12 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>255</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -933,13 +933,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P74"/>
+  <dimension ref="A1:P83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -2350,32 +2350,32 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33012</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE GRASSE</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J23" s="11" t="n">
@@ -2401,19 +2401,19 @@
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33021</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165368</t>
         </is>
       </c>
       <c r="N23" s="12" t="n">
-        <v>2000</v>
-      </c>
-      <c r="O23" s="13" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O23" s="12" t="n">
+        <v>1079</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
@@ -2422,32 +2422,32 @@
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32848</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRENOBLE] - Modification modèles de facture</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRENOBLE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>Modification modèles de facture</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F24" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G24" s="15" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="I24" s="15" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J24" s="15" t="n">
@@ -2473,16 +2473,16 @@
       </c>
       <c r="L24" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32852</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M24" s="15" t="inlineStr">
         <is>
-          <t>00164564</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N24" s="16" t="n">
-        <v>300</v>
+        <v>2000</v>
       </c>
       <c r="O24" s="13" t="n">
         <v>0</v>
@@ -2494,12 +2494,12 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32831</t>
+          <t>PDMDEP-32848</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE PANTIN] - Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
+          <t>[COMMUNE DE GRENOBLE] - Modification modèles de facture</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE PANTIN</t>
+          <t>COMMUNE DE GRENOBLE</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
+          <t>Modification modèles de facture</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="J25" s="11" t="n">
@@ -2545,16 +2545,16 @@
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32837</t>
+          <t>PDMDEP-32852</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>00164275</t>
+          <t>00164564</t>
         </is>
       </c>
       <c r="N25" s="12" t="n">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="O25" s="13" t="n">
         <v>0</v>
@@ -2566,32 +2566,32 @@
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-32831</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[COMMUNE DE PANTIN] - Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>COMMUNE DE PANTIN</t>
         </is>
       </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
         </is>
       </c>
       <c r="F26" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G26" s="15" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="I26" s="15" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="J26" s="15" t="n">
@@ -2617,16 +2617,16 @@
       </c>
       <c r="L26" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32837</t>
         </is>
       </c>
       <c r="M26" s="15" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00164275</t>
         </is>
       </c>
       <c r="N26" s="16" t="n">
-        <v>705</v>
+        <v>900</v>
       </c>
       <c r="O26" s="13" t="n">
         <v>0</v>
@@ -2638,12 +2638,12 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32759</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE DU GRAND REIMS - DSIT] - MV app/ infra + màj carto</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE DU GRAND REIMS - DSIT</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
@@ -2689,16 +2689,16 @@
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32763</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>00163805</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N27" s="12" t="n">
-        <v>564</v>
+        <v>705</v>
       </c>
       <c r="O27" s="13" t="n">
         <v>0</v>
@@ -2710,32 +2710,32 @@
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32732</t>
+          <t>PDMDEP-32759</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
+          <t>[COMMUNAUTE URBAINE DU GRAND REIMS - DSIT] - MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA SENTINELLE</t>
+          <t>COMMUNAUTE URBAINE DU GRAND REIMS - DSIT</t>
         </is>
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Caisse</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F28" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G28" s="15" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H28" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I28" s="15" t="inlineStr">
@@ -2761,16 +2761,16 @@
       </c>
       <c r="L28" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32741</t>
+          <t>PDMDEP-32763</t>
         </is>
       </c>
       <c r="M28" s="15" t="inlineStr">
         <is>
-          <t>00163789</t>
+          <t>00163805</t>
         </is>
       </c>
       <c r="N28" s="16" t="n">
-        <v>2138.2</v>
+        <v>564</v>
       </c>
       <c r="O28" s="13" t="n">
         <v>0</v>
@@ -2782,12 +2782,12 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32703</t>
+          <t>PDMDEP-32732</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[MAIRIE DE MIRIBEL] - MIGRATION PLACIER SIMPLE + PAX </t>
+          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE MIRIBEL</t>
+          <t>MAIRIE DE LA SENTINELLE</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION PLACIER SIMPLE + PAX </t>
+          <t>Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J29" s="11" t="n">
@@ -2833,16 +2833,16 @@
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32712</t>
+          <t>PDMDEP-32741</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>00163498</t>
+          <t>00163789</t>
         </is>
       </c>
       <c r="N29" s="12" t="n">
-        <v>283.5</v>
+        <v>2138.2</v>
       </c>
       <c r="O29" s="13" t="n">
         <v>0</v>
@@ -2854,32 +2854,32 @@
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32703</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t xml:space="preserve">[MAIRIE DE MIRIBEL] - MIGRATION PLACIER SIMPLE + PAX </t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>MAIRIE DE MIRIBEL</t>
         </is>
       </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">MIGRATION PLACIER SIMPLE + PAX </t>
         </is>
       </c>
       <c r="F30" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G30" s="15" t="inlineStr">
@@ -2889,12 +2889,12 @@
       </c>
       <c r="H30" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I30" s="15" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="J30" s="15" t="n">
@@ -2905,16 +2905,16 @@
       </c>
       <c r="L30" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32712</t>
         </is>
       </c>
       <c r="M30" s="15" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00163498</t>
         </is>
       </c>
       <c r="N30" s="16" t="n">
-        <v>548.4</v>
+        <v>283.5</v>
       </c>
       <c r="O30" s="13" t="n">
         <v>0</v>
@@ -2926,32 +2926,32 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32598</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Déploiement GeoDP Caisse</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
@@ -2973,20 +2973,20 @@
         <v>3</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32607</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>00163155</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N31" s="12" t="n">
-        <v>552</v>
+        <v>548.4</v>
       </c>
       <c r="O31" s="13" t="n">
         <v>0</v>
@@ -2998,27 +2998,27 @@
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32598</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="F32" s="15" t="inlineStr">
@@ -3033,32 +3033,32 @@
       </c>
       <c r="H32" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I32" s="15" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J32" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K32" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32607</t>
         </is>
       </c>
       <c r="M32" s="15" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00163155</t>
         </is>
       </c>
       <c r="N32" s="16" t="n">
-        <v>1868</v>
+        <v>552</v>
       </c>
       <c r="O32" s="13" t="n">
         <v>0</v>
@@ -3070,32 +3070,32 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod </t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J33" s="11" t="n">
@@ -3121,16 +3121,16 @@
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>00161842</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N33" s="12" t="n">
-        <v>882.5</v>
+        <v>1868</v>
       </c>
       <c r="O33" s="13" t="n">
         <v>0</v>
@@ -3142,32 +3142,32 @@
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t xml:space="preserve">[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E34" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F34" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G34" s="15" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="H34" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I34" s="15" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J34" s="15" t="n">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="L34" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="M34" s="15" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161842</t>
         </is>
       </c>
       <c r="N34" s="16" t="n">
-        <v>450</v>
+        <v>882.5</v>
       </c>
       <c r="O34" s="13" t="n">
         <v>0</v>
@@ -3214,32 +3214,32 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J35" s="11" t="n">
@@ -3265,16 +3265,16 @@
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N35" s="12" t="n">
-        <v>1046.5</v>
+        <v>450</v>
       </c>
       <c r="O35" s="13" t="n">
         <v>0</v>
@@ -3286,32 +3286,32 @@
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E36" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F36" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G36" s="15" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="H36" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I36" s="15" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J36" s="15" t="n">
@@ -3337,16 +3337,16 @@
       </c>
       <c r="L36" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M36" s="15" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N36" s="16" t="n">
-        <v>250</v>
+        <v>1046.5</v>
       </c>
       <c r="O36" s="13" t="n">
         <v>0</v>
@@ -3358,27 +3358,27 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J37" s="11" t="n">
@@ -3409,16 +3409,16 @@
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>407</v>
+        <v>250</v>
       </c>
       <c r="O37" s="13" t="n">
         <v>0</v>
@@ -3430,32 +3430,32 @@
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E38" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F38" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G38" s="15" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="I38" s="15" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J38" s="15" t="n">
@@ -3481,16 +3481,16 @@
       </c>
       <c r="L38" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M38" s="15" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N38" s="16" t="n">
-        <v>440.38</v>
+        <v>407</v>
       </c>
       <c r="O38" s="13" t="n">
         <v>0</v>
@@ -3502,32 +3502,32 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J39" s="11" t="n">
@@ -3553,16 +3553,16 @@
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>285</v>
+        <v>440.38</v>
       </c>
       <c r="O39" s="13" t="n">
         <v>0</v>
@@ -3574,32 +3574,32 @@
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E40" s="15" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F40" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G40" s="15" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="I40" s="15" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J40" s="15" t="n">
@@ -3625,16 +3625,16 @@
       </c>
       <c r="L40" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M40" s="15" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N40" s="16" t="n">
-        <v>2650</v>
+        <v>285</v>
       </c>
       <c r="O40" s="13" t="n">
         <v>0</v>
@@ -3646,12 +3646,12 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
@@ -3661,12 +3661,12 @@
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J41" s="11" t="n">
@@ -3697,16 +3697,16 @@
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
-        <v>120</v>
+        <v>2650</v>
       </c>
       <c r="O41" s="13" t="n">
         <v>0</v>
@@ -3718,32 +3718,32 @@
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E42" s="15" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F42" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G42" s="15" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="H42" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I42" s="15" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J42" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K42" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M42" s="15" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N42" s="16" t="n">
-        <v>203.5</v>
+        <v>120</v>
       </c>
       <c r="O42" s="13" t="n">
         <v>0</v>
@@ -3790,12 +3790,12 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
@@ -3805,12 +3805,12 @@
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
@@ -3841,16 +3841,16 @@
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
-        <v>150</v>
+        <v>203.5</v>
       </c>
       <c r="O43" s="13" t="n">
         <v>0</v>
@@ -3862,32 +3862,32 @@
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C44" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E44" s="15" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F44" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G44" s="15" t="inlineStr">
@@ -3897,32 +3897,32 @@
       </c>
       <c r="H44" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I44" s="15" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J44" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K44" s="15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L44" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M44" s="15" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N44" s="16" t="n">
-        <v>3288.55</v>
+        <v>150</v>
       </c>
       <c r="O44" s="13" t="n">
         <v>0</v>
@@ -3934,32 +3934,32 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
@@ -3969,32 +3969,32 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>210</v>
+        <v>3288.55</v>
       </c>
       <c r="O45" s="13" t="n">
         <v>0</v>
@@ -4006,27 +4006,27 @@
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31285</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LUNEL] - FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>Valentin CAUJOLLE</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LUNEL</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E46" s="15" t="inlineStr">
         <is>
-          <t>FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F46" s="15" t="inlineStr">
@@ -4046,29 +4046,29 @@
       </c>
       <c r="I46" s="15" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J46" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K46" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L46" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31289</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M46" s="15" t="inlineStr">
         <is>
-          <t>00156834</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N46" s="16" t="n">
-        <v>71.2</v>
-      </c>
-      <c r="O46" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P46" s="16" t="n">
@@ -4078,12 +4078,12 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J47" s="11" t="n">
@@ -4129,16 +4129,16 @@
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="O47" s="13" t="n">
         <v>0</v>
@@ -4150,32 +4150,32 @@
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31285</t>
         </is>
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE DE LUNEL] - FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
         </is>
       </c>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Valentin CAUJOLLE</t>
         </is>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE DE LUNEL</t>
         </is>
       </c>
       <c r="E48" s="15" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
         </is>
       </c>
       <c r="F48" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G48" s="15" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="H48" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I48" s="15" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>16/02/2026</t>
         </is>
       </c>
       <c r="J48" s="15" t="n">
@@ -4201,16 +4201,16 @@
       </c>
       <c r="L48" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31289</t>
         </is>
       </c>
       <c r="M48" s="15" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156834</t>
         </is>
       </c>
       <c r="N48" s="16" t="n">
-        <v>255</v>
+        <v>71.2</v>
       </c>
       <c r="O48" s="13" t="n">
         <v>0</v>
@@ -4222,12 +4222,12 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30358</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARGELES-SUR-MER</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -4262,27 +4262,27 @@
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K49" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30366</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00154569</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="O49" s="13" t="n">
         <v>0</v>
@@ -4294,12 +4294,12 @@
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C50" s="15" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F50" s="15" t="inlineStr">
@@ -4334,27 +4334,27 @@
       </c>
       <c r="I50" s="15" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J50" s="15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K50" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M50" s="15" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N50" s="16" t="n">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="O50" s="13" t="n">
         <v>0</v>
@@ -4366,27 +4366,27 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30311</t>
+          <t>PDMDEP-30358</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CAEN] - GeODP - Modification des marges via activation Editique</t>
+          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAEN</t>
+          <t>COMMUNE D'ARGELES-SUR-MER</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>GeODP - Modification des marges via activation Editique</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="J51" s="11" t="n">
@@ -4417,16 +4417,16 @@
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30316</t>
+          <t>PDMDEP-30366</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00154362</t>
+          <t>00154569</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="O51" s="13" t="n">
         <v>0</v>
@@ -4438,32 +4438,32 @@
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30062</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C52" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>Commune de Saint-Dizier</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E52" s="15" t="inlineStr">
         <is>
-          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F52" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G52" s="15" t="inlineStr">
@@ -4473,12 +4473,12 @@
       </c>
       <c r="H52" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I52" s="15" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J52" s="15" t="n">
@@ -4489,16 +4489,16 @@
       </c>
       <c r="L52" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30063</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M52" s="15" t="inlineStr">
         <is>
-          <t>00153633</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N52" s="16" t="n">
-        <v>350</v>
+        <v>140</v>
       </c>
       <c r="O52" s="13" t="n">
         <v>0</v>
@@ -4510,32 +4510,32 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-30311</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t>[COMMUNE DE CAEN] - GeODP - Modification des marges via activation Editique</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>COMMUNE DE CAEN</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t>GeODP - Modification des marges via activation Editique</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
@@ -4545,34 +4545,34 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-30316</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00154362</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" s="12" t="n">
+        <v>200</v>
+      </c>
+      <c r="O53" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P53" s="12" t="n">
@@ -4582,12 +4582,12 @@
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29122</t>
+          <t>PDMDEP-30062</t>
         </is>
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES DEUX SEVRES (CD 79) - LITTERALIS - Flux WFS communication</t>
+          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="C54" s="15" t="inlineStr">
@@ -4597,11 +4597,13 @@
       </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES DEUX SEVRES (CD 79)</t>
-        </is>
-      </c>
-      <c r="E54" s="15" t="n">
-        <v/>
+          <t>Commune de Saint-Dizier</t>
+        </is>
+      </c>
+      <c r="E54" s="15" t="inlineStr">
+        <is>
+          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
+        </is>
       </c>
       <c r="F54" s="15" t="inlineStr">
         <is>
@@ -4620,27 +4622,27 @@
       </c>
       <c r="I54" s="15" t="inlineStr">
         <is>
-          <t>19/12/2025</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="J54" s="15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K54" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29124</t>
+          <t>PDMDEP-30063</t>
         </is>
       </c>
       <c r="M54" s="15" t="inlineStr">
         <is>
-          <t>00148148</t>
+          <t>00153633</t>
         </is>
       </c>
       <c r="N54" s="16" t="n">
-        <v>157.5</v>
+        <v>350</v>
       </c>
       <c r="O54" s="13" t="n">
         <v>0</v>
@@ -4652,26 +4654,28 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E55" s="11" t="n">
-        <v/>
+          <t>MAIRE DE PONTARLIER</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
+        </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
@@ -4685,34 +4689,34 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>2812.32</v>
-      </c>
-      <c r="O55" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P55" s="12" t="n">
@@ -4722,27 +4726,27 @@
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C56" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E56" s="15" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F56" s="15" t="inlineStr">
@@ -4757,34 +4761,34 @@
       </c>
       <c r="H56" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I56" s="15" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J56" s="15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K56" s="15" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="L56" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M56" s="15" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N56" s="16" t="n">
-        <v>392.5</v>
-      </c>
-      <c r="O56" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P56" s="16" t="n">
@@ -4794,27 +4798,27 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
@@ -4829,34 +4833,34 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>1556.25</v>
-      </c>
-      <c r="O57" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P57" s="12" t="n">
@@ -4866,27 +4870,27 @@
     <row r="58">
       <c r="A58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C58" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E58" s="15" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F58" s="15" t="inlineStr">
@@ -4901,34 +4905,34 @@
       </c>
       <c r="H58" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I58" s="15" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J58" s="15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K58" s="15" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="L58" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M58" s="15" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N58" s="16" t="n">
-        <v>1790</v>
-      </c>
-      <c r="O58" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P58" s="16" t="n">
@@ -4938,12 +4942,12 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-29122</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>DEPARTEMENT DES DEUX SEVRES (CD 79) - LITTERALIS - Flux WFS communication</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
@@ -4953,7 +4957,7 @@
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
+          <t>DEPARTEMENT DES DEUX SEVRES (CD 79)</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
@@ -4971,32 +4975,32 @@
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>19/12/2025</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K59" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-29124</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00148148</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
-        <v>732</v>
+        <v>157.5</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>0</v>
@@ -5008,28 +5012,26 @@
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-26782</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C60" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
-        </is>
-      </c>
-      <c r="E60" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement LiEx</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E60" s="15" t="n">
+        <v/>
       </c>
       <c r="F60" s="15" t="inlineStr">
         <is>
@@ -5048,29 +5050,29 @@
       </c>
       <c r="I60" s="15" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J60" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K60" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L60" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-26783</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M60" s="15" t="inlineStr">
         <is>
-          <t>00142659</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N60" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" s="16" t="n">
+        <v>2812.32</v>
+      </c>
+      <c r="O60" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P60" s="16" t="n">
@@ -5080,12 +5082,12 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
@@ -5095,11 +5097,13 @@
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
-        </is>
-      </c>
-      <c r="E61" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
@@ -5118,27 +5122,27 @@
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K61" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
-        <v>1212</v>
+        <v>392.5</v>
       </c>
       <c r="O61" s="13" t="n">
         <v>0</v>
@@ -5150,12 +5154,12 @@
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C62" s="15" t="inlineStr">
@@ -5165,11 +5169,13 @@
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
-        </is>
-      </c>
-      <c r="E62" s="15" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E62" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F62" s="15" t="inlineStr">
         <is>
@@ -5188,27 +5194,27 @@
       </c>
       <c r="I62" s="15" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J62" s="15" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K62" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L62" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M62" s="15" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N62" s="16" t="n">
-        <v>2323</v>
+        <v>1556.25</v>
       </c>
       <c r="O62" s="13" t="n">
         <v>0</v>
@@ -5220,30 +5226,32 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23484</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- AJOUT LIEU DE NAISSANCE DANS FILIEN</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
-        </is>
-      </c>
-      <c r="E63" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr">
@@ -5253,32 +5261,32 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>25/07/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K63" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27494</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>495695</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
-        <v>140.4</v>
+        <v>1790</v>
       </c>
       <c r="O63" s="13" t="n">
         <v>0</v>
@@ -5290,22 +5298,22 @@
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22996</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
         </is>
       </c>
       <c r="E64" s="15" t="n">
@@ -5323,34 +5331,34 @@
       </c>
       <c r="H64" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J64" s="15" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K64" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L64" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28051</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M64" s="15" t="inlineStr">
         <is>
-          <t>487190</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N64" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" s="16" t="n">
+        <v>732</v>
+      </c>
+      <c r="O64" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P64" s="16" t="n">
@@ -5360,30 +5368,32 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21546</t>
+          <t>PDMDEP-26782</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
+          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>VILLEURBANNE</t>
-        </is>
-      </c>
-      <c r="E65" s="11" t="n">
-        <v/>
+          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement LiEx</t>
+        </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
@@ -5393,34 +5403,34 @@
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>05/05/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28038</t>
+          <t>PDMDEP-26783</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>478867</t>
+          <t>00142659</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>1413.6</v>
-      </c>
-      <c r="O65" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P65" s="12" t="n">
@@ -5430,12 +5440,12 @@
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
@@ -5445,7 +5455,7 @@
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E66" s="15" t="n">
@@ -5463,32 +5473,32 @@
       </c>
       <c r="H66" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I66" s="15" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J66" s="15" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K66" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L66" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M66" s="15" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N66" s="16" t="n">
-        <v>250</v>
+        <v>1212</v>
       </c>
       <c r="O66" s="13" t="n">
         <v>0</v>
@@ -5500,12 +5510,12 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
@@ -5515,7 +5525,7 @@
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>VILLE DE DRANCY</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
@@ -5538,29 +5548,29 @@
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-27028</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>460</v>
-      </c>
-      <c r="O67" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P67" s="12" t="n">
@@ -5570,22 +5580,22 @@
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19385</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARCUEIL</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E68" s="15" t="n">
@@ -5608,29 +5618,29 @@
       </c>
       <c r="I68" s="15" t="inlineStr">
         <is>
-          <t>24/02/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J68" s="15" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="K68" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L68" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27535</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M68" s="15" t="inlineStr">
         <is>
-          <t>465345</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N68" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" s="16" t="n">
+        <v>2323</v>
+      </c>
+      <c r="O68" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P68" s="16" t="n">
@@ -5640,12 +5650,12 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-23484</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>METROPOLE TOULON- AJOUT LIEU DE NAISSANCE DANS FILIEN</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
@@ -5655,7 +5665,7 @@
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
@@ -5673,32 +5683,32 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>25/07/2025</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="K69" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-27494</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>495695</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>240</v>
+        <v>140.4</v>
       </c>
       <c r="O69" s="13" t="n">
         <v>0</v>
@@ -5710,12 +5720,12 @@
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-22996</t>
         </is>
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
@@ -5725,7 +5735,7 @@
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E70" s="15" t="n">
@@ -5748,23 +5758,23 @@
       </c>
       <c r="I70" s="15" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="J70" s="15" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="K70" s="15" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="L70" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28020</t>
+          <t>PDMDEP-28051</t>
         </is>
       </c>
       <c r="M70" s="15" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>487190</t>
         </is>
       </c>
       <c r="N70" s="16" t="n">
@@ -5780,12 +5790,12 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-16868</t>
+          <t>PDMDEP-21546</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>[Limoges] migration placier</t>
+          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
@@ -5795,7 +5805,7 @@
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>Limoges</t>
+          <t>VILLEURBANNE</t>
         </is>
       </c>
       <c r="E71" s="11" t="n">
@@ -5808,31 +5818,39 @@
       </c>
       <c r="G71" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>26/09/2024</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L71" s="11" t="inlineStr"/>
-      <c r="M71" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L71" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28038</t>
+        </is>
+      </c>
+      <c r="M71" s="11" t="inlineStr">
+        <is>
+          <t>478867</t>
+        </is>
+      </c>
       <c r="N71" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" s="12" t="n">
+        <v>1413.6</v>
+      </c>
+      <c r="O71" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P71" s="12" t="n">
@@ -5842,21 +5860,27 @@
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="C72" s="15" t="inlineStr"/>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+        </is>
+      </c>
+      <c r="C72" s="15" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="E72" s="15" t="inlineStr"/>
+          <t>MONTREUIL</t>
+        </is>
+      </c>
+      <c r="E72" s="15" t="n">
+        <v/>
+      </c>
       <c r="F72" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -5867,30 +5891,34 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H72" s="15" t="inlineStr"/>
+      <c r="H72" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I72" s="15" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J72" s="15" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="K72" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L72" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33362</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M72" s="15" t="inlineStr">
         <is>
-          <t>00167140</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N72" s="16" t="n">
-        <v>510.6</v>
+        <v>250</v>
       </c>
       <c r="O72" s="13" t="n">
         <v>0</v>
@@ -5902,89 +5930,687 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
+          <t>PDMDEP-20907</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>SAINT PIERRE (LA REUNION)</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F73" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G73" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H73" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>14/04/2025</t>
+        </is>
+      </c>
+      <c r="J73" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="K73" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M73" s="11" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
+      <c r="N73" s="12" t="n">
+        <v>460</v>
+      </c>
+      <c r="O73" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-19792</t>
+        </is>
+      </c>
+      <c r="B74" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+        </is>
+      </c>
+      <c r="C74" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D74" s="15" t="inlineStr">
+        <is>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+        </is>
+      </c>
+      <c r="E74" s="15" t="n">
+        <v/>
+      </c>
+      <c r="F74" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G74" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H74" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I74" s="15" t="inlineStr">
+        <is>
+          <t>06/03/2025</t>
+        </is>
+      </c>
+      <c r="J74" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="K74" s="15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L74" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27377</t>
+        </is>
+      </c>
+      <c r="M74" s="15" t="inlineStr">
+        <is>
+          <t>478048</t>
+        </is>
+      </c>
+      <c r="N74" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-19385</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
+        </is>
+      </c>
+      <c r="C75" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>COMMUNE D'ARCUEIL</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F75" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G75" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H75" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I75" s="11" t="inlineStr">
+        <is>
+          <t>24/02/2025</t>
+        </is>
+      </c>
+      <c r="J75" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="K75" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L75" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27535</t>
+        </is>
+      </c>
+      <c r="M75" s="11" t="inlineStr">
+        <is>
+          <t>465345</t>
+        </is>
+      </c>
+      <c r="N75" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-18115</t>
+        </is>
+      </c>
+      <c r="B76" s="15" t="inlineStr">
+        <is>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
+        </is>
+      </c>
+      <c r="C76" s="15" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="D76" s="15" t="inlineStr">
+        <is>
+          <t>BISCHWILLER</t>
+        </is>
+      </c>
+      <c r="E76" s="15" t="n">
+        <v/>
+      </c>
+      <c r="F76" s="15" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="G76" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H76" s="15" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="I76" s="15" t="inlineStr">
+        <is>
+          <t>17/12/2024</t>
+        </is>
+      </c>
+      <c r="J76" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="K76" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M76" s="15" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
+      <c r="N76" s="16" t="n">
+        <v>240</v>
+      </c>
+      <c r="O76" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-18038</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t>[CD 38] Reprise de 1644 AP</t>
+        </is>
+      </c>
+      <c r="C77" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F77" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G77" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H77" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I77" s="11" t="inlineStr">
+        <is>
+          <t>12/12/2024</t>
+        </is>
+      </c>
+      <c r="J77" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="K77" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L77" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28020</t>
+        </is>
+      </c>
+      <c r="M77" s="11" t="inlineStr">
+        <is>
+          <t>458057</t>
+        </is>
+      </c>
+      <c r="N77" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-16868</t>
+        </is>
+      </c>
+      <c r="B78" s="15" t="inlineStr">
+        <is>
+          <t>[Limoges] migration placier</t>
+        </is>
+      </c>
+      <c r="C78" s="15" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="D78" s="15" t="inlineStr">
+        <is>
+          <t>Limoges</t>
+        </is>
+      </c>
+      <c r="E78" s="15" t="n">
+        <v/>
+      </c>
+      <c r="F78" s="15" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="G78" s="15" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H78" s="15" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="I78" s="15" t="inlineStr">
+        <is>
+          <t>26/09/2024</t>
+        </is>
+      </c>
+      <c r="J78" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="K78" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L78" s="15" t="inlineStr"/>
+      <c r="M78" s="15" t="inlineStr"/>
+      <c r="N78" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-14551</t>
+        </is>
+      </c>
+      <c r="B79" s="11" t="inlineStr">
+        <is>
+          <t>[Perpignan] Interface formulaire</t>
+        </is>
+      </c>
+      <c r="C79" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>[Perpignan]</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F79" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G79" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H79" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I79" s="11" t="inlineStr">
+        <is>
+          <t>14/03/2024</t>
+        </is>
+      </c>
+      <c r="J79" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="K79" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L79" s="11" t="inlineStr"/>
+      <c r="M79" s="11" t="inlineStr"/>
+      <c r="N79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-12222</t>
+        </is>
+      </c>
+      <c r="B80" s="15" t="inlineStr">
+        <is>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C80" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D80" s="15" t="inlineStr">
+        <is>
+          <t>CD14</t>
+        </is>
+      </c>
+      <c r="E80" s="15" t="inlineStr">
+        <is>
+          <t>Modélisation spécifique</t>
+        </is>
+      </c>
+      <c r="F80" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G80" s="15" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H80" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I80" s="15" t="inlineStr">
+        <is>
+          <t>04/09/2023</t>
+        </is>
+      </c>
+      <c r="J80" s="15" t="n">
+        <v>34</v>
+      </c>
+      <c r="K80" s="15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L80" s="15" t="inlineStr"/>
+      <c r="M80" s="15" t="inlineStr"/>
+      <c r="N80" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>PSC-1270</t>
+        </is>
+      </c>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="C81" s="11" t="inlineStr"/>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="inlineStr"/>
+      <c r="F81" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G81" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H81" s="11" t="inlineStr"/>
+      <c r="I81" s="11" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J81" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K81" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M81" s="11" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N81" s="12" t="n">
+        <v>510.6</v>
+      </c>
+      <c r="O81" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="14" t="inlineStr">
+        <is>
           <t>PSC-1228</t>
         </is>
       </c>
-      <c r="B73" s="11" t="inlineStr">
+      <c r="B82" s="15" t="inlineStr">
         <is>
           <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
-      <c r="C73" s="11" t="inlineStr"/>
-      <c r="D73" s="11" t="inlineStr">
+      <c r="C82" s="15" t="inlineStr"/>
+      <c r="D82" s="15" t="inlineStr">
         <is>
           <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
-      <c r="E73" s="11" t="inlineStr"/>
-      <c r="F73" s="11" t="inlineStr">
+      <c r="E82" s="15" t="inlineStr"/>
+      <c r="F82" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G73" s="11" t="inlineStr">
+      <c r="G82" s="15" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H73" s="11" t="inlineStr"/>
-      <c r="I73" s="11" t="inlineStr">
+      <c r="H82" s="15" t="inlineStr"/>
+      <c r="I82" s="15" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="J73" s="11" t="n">
+      <c r="J82" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="K73" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" s="11" t="inlineStr">
+      <c r="K82" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="15" t="inlineStr">
         <is>
           <t>PDMDEP-32829</t>
         </is>
       </c>
-      <c r="M73" s="11" t="inlineStr">
+      <c r="M82" s="15" t="inlineStr">
         <is>
           <t>00163534</t>
         </is>
       </c>
-      <c r="N73" s="12" t="n">
+      <c r="N82" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="O73" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="17" t="inlineStr">
+      <c r="O82" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B74" s="17" t="inlineStr"/>
-      <c r="C74" s="17" t="inlineStr"/>
-      <c r="D74" s="17" t="inlineStr"/>
-      <c r="E74" s="17" t="inlineStr"/>
-      <c r="F74" s="17" t="inlineStr"/>
-      <c r="G74" s="17" t="inlineStr"/>
-      <c r="H74" s="17" t="inlineStr"/>
-      <c r="I74" s="17" t="inlineStr"/>
-      <c r="J74" s="17" t="inlineStr"/>
-      <c r="K74" s="17" t="inlineStr"/>
-      <c r="L74" s="17" t="inlineStr"/>
-      <c r="M74" s="17" t="inlineStr"/>
-      <c r="N74" s="18" t="n">
+      <c r="B83" s="17" t="inlineStr"/>
+      <c r="C83" s="17" t="inlineStr"/>
+      <c r="D83" s="17" t="inlineStr"/>
+      <c r="E83" s="17" t="inlineStr"/>
+      <c r="F83" s="17" t="inlineStr"/>
+      <c r="G83" s="17" t="inlineStr"/>
+      <c r="H83" s="17" t="inlineStr"/>
+      <c r="I83" s="17" t="inlineStr"/>
+      <c r="J83" s="17" t="inlineStr"/>
+      <c r="K83" s="17" t="inlineStr"/>
+      <c r="L83" s="17" t="inlineStr"/>
+      <c r="M83" s="17" t="inlineStr"/>
+      <c r="N83" s="18" t="n">
         <v>56751.68</v>
       </c>
-      <c r="O74" s="18" t="n">
-        <v>219.1</v>
-      </c>
-      <c r="P74" s="18" t="n">
-        <v>30.22</v>
+      <c r="O83" s="18" t="n">
+        <v>1298.1</v>
+      </c>
+      <c r="P83" s="18" t="n">
+        <v>144.39</v>
       </c>
     </row>
   </sheetData>
@@ -6059,6 +6685,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId78"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6633,16 +7268,16 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>6.75</v>
+        <v>8</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>6.75</v>
+        <v>8.5</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>0</v>
@@ -6652,7 +7287,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1.7%</t>
         </is>
       </c>
     </row>
@@ -6694,7 +7329,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
     </row>
   </sheetData>
@@ -6779,16 +7414,16 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>394300</v>
+        <v>393221</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>191462</v>
+        <v>191962</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>202838</v>
+        <v>201259</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>171478</v>
+        <v>169899</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>15760</v>
@@ -6807,13 +7442,13 @@
         <v>187891</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>83387</v>
+        <v>83887</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>104505</v>
+        <v>104005</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>96996</v>
+        <v>96496</v>
       </c>
       <c r="F6" s="25" t="n">
         <v>3060</v>
@@ -6829,16 +7464,16 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>206409</v>
+        <v>205330</v>
       </c>
       <c r="C7" s="26" t="n">
         <v>108075</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>98333</v>
+        <v>97254</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>74482</v>
+        <v>73403</v>
       </c>
       <c r="F7" s="26" t="n">
         <v>12700</v>
@@ -6858,7 +7493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -6882,7 +7517,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 1 commande(s)</t>
+          <t>Épics créées ce mois — 2 commande(s)</t>
         </is>
       </c>
     </row>
@@ -6937,73 +7572,97 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
+          <t>PDMDEP-34396</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34390</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>Commune Le THOR</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H5" s="15" t="inlineStr">
+        <is>
+          <t>00171793</t>
+        </is>
+      </c>
+      <c r="I5" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
           <t>PDMDEP-34362</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-34358</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>01/07/2026</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F5" s="15" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G5" s="15" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H5" s="15" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
         <is>
           <t>458057</t>
         </is>
       </c>
-      <c r="I5" s="25" t="n">
+      <c r="I6" s="26" t="n">
         <v>6806.25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="n"/>
-      <c r="C6" s="17" t="n"/>
-      <c r="D6" s="17" t="n"/>
-      <c r="E6" s="17" t="n"/>
-      <c r="F6" s="17" t="n"/>
-      <c r="G6" s="17" t="n"/>
-      <c r="H6" s="17" t="inlineStr">
-        <is>
-          <t>1 commande(s)</t>
-        </is>
-      </c>
-      <c r="I6" s="24" t="n">
-        <v>6806</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B7" s="17" t="n"/>
@@ -7014,7 +7673,7 @@
       <c r="G7" s="17" t="n"/>
       <c r="H7" s="17" t="inlineStr">
         <is>
-          <t>1 commande(s)</t>
+          <t>2 commande(s)</t>
         </is>
       </c>
       <c r="I7" s="24" t="n">
@@ -7024,7 +7683,7 @@
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B8" s="17" t="n"/>
@@ -7035,10 +7694,31 @@
       <c r="G8" s="17" t="n"/>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t>0 commande(s)</t>
+          <t>1 commande(s)</t>
         </is>
       </c>
       <c r="I8" s="24" t="n">
+        <v>6806</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
+      <c r="G9" s="17" t="n"/>
+      <c r="H9" s="17" t="inlineStr">
+        <is>
+          <t>1 commande(s)</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="n">
         <v>0</v>
       </c>
     </row>

--- a/jira_export_2026-07-01.xlsx
+++ b/jira_export_2026-07-01.xlsx
@@ -30,7 +30,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.00 &quot;€&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0 €"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -112,6 +112,12 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00C00000"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00375623"/>
       <sz val="18"/>
     </font>
   </fonts>
@@ -226,7 +232,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -242,6 +248,9 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -252,14 +261,14 @@
     <xf numFmtId="164" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -815,7 +824,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>12 h</t>
+          <t>38 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -827,9 +836,9 @@
       </c>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>29.4%</t>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P83"/>
+  <dimension ref="A1:P91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -942,13 +951,13 @@
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
@@ -970,168 +979,168 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Epic Nom</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Assigné</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>Solution</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>Type de deal</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="10" t="inlineStr">
         <is>
           <t>Date commande</t>
         </is>
       </c>
-      <c r="J4" s="9" t="inlineStr">
+      <c r="J4" s="10" t="inlineStr">
         <is>
           <t>Ancienneté (mois)</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="10" t="inlineStr">
         <is>
           <t>Temps mois (h)</t>
         </is>
       </c>
-      <c r="L4" s="9" t="inlineStr">
+      <c r="L4" s="10" t="inlineStr">
         <is>
           <t>Ticket CA</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="M4" s="10" t="inlineStr">
         <is>
           <t>Numéro BDC</t>
         </is>
       </c>
-      <c r="N4" s="9" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>Prévision du mois</t>
         </is>
       </c>
-      <c r="O4" s="9" t="inlineStr">
+      <c r="O4" s="10" t="inlineStr">
         <is>
           <t>Montant déclaré ce mois</t>
         </is>
       </c>
-      <c r="P4" s="9" t="inlineStr">
+      <c r="P4" s="10" t="inlineStr">
         <is>
           <t>Rentabilité (€ / h)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-34081</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>[COMMUNE DE ERQUY] - Migration GEODP 2 + Pax</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Quentin BORDILLON</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>COMMUNE DE ERQUY</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>Migration GEODP 2 + Pax</t>
-        </is>
-      </c>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>GEODP</t>
-        </is>
-      </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34229</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>DIJON METROPOLE</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>GRC + Connecteur</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
-        <is>
-          <t>Migration</t>
-        </is>
-      </c>
-      <c r="I5" s="11" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="J5" s="11" t="n">
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34090</t>
-        </is>
-      </c>
-      <c r="M5" s="11" t="inlineStr">
-        <is>
-          <t>00170724</t>
-        </is>
-      </c>
-      <c r="N5" s="12" t="n">
-        <v>1242.5</v>
+      <c r="K5" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-34235</t>
+        </is>
+      </c>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>00171333</t>
+        </is>
+      </c>
+      <c r="N5" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="O5" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="P5" s="12" t="n">
+      <c r="P5" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
@@ -1141,12 +1150,12 @@
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F6" s="15" t="inlineStr">
@@ -1161,34 +1170,34 @@
       </c>
       <c r="H6" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J6" s="15" t="n">
         <v>1</v>
       </c>
       <c r="K6" s="15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L6" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="M6" s="15" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="N6" s="16" t="n">
-        <v>2100</v>
-      </c>
-      <c r="O6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P6" s="16" t="n">
@@ -1196,106 +1205,106 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-33906</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Alizée MARGOT</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>Commune d'Arras</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>Migration GEODP ODP (Terrasse)</t>
-        </is>
-      </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34081</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>[COMMUNE DE ERQUY] - Migration GEODP 2 + Pax</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Quentin BORDILLON</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE DE ERQUY</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>Migration GEODP 2 + Pax</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>GEODP</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr">
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t>Migration</t>
         </is>
       </c>
-      <c r="I7" s="11" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="J7" s="11" t="n">
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J7" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-33914</t>
-        </is>
-      </c>
-      <c r="M7" s="11" t="inlineStr">
-        <is>
-          <t>00167633</t>
-        </is>
-      </c>
-      <c r="N7" s="12" t="n">
-        <v>2100</v>
-      </c>
-      <c r="O7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="12" t="n">
+      <c r="K7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-34090</t>
+        </is>
+      </c>
+      <c r="M7" s="12" t="inlineStr">
+        <is>
+          <t>00170724</t>
+        </is>
+      </c>
+      <c r="N7" s="13" t="n">
+        <v>1242.5</v>
+      </c>
+      <c r="O7" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F8" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G8" s="15" t="inlineStr">
@@ -1310,136 +1319,136 @@
       </c>
       <c r="I8" s="15" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J8" s="15" t="n">
         <v>1</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L8" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M8" s="15" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N8" s="16" t="n">
-        <v>657.3</v>
-      </c>
-      <c r="O8" s="13" t="n">
-        <v>219.1</v>
+        <v>2100</v>
+      </c>
+      <c r="O8" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>175.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-33804</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>Fabien REUTENAUER</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>Purge arrêtés temporaires</t>
-        </is>
-      </c>
-      <c r="F9" s="11" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33906</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Commune d'Arras</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>Migration GEODP ODP (Terrasse)</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H9" s="11" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
-      <c r="I9" s="11" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="J9" s="11" t="n">
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J9" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-33808</t>
-        </is>
-      </c>
-      <c r="M9" s="11" t="inlineStr">
-        <is>
-          <t>00169856</t>
-        </is>
-      </c>
-      <c r="N9" s="12" t="n">
-        <v>1890</v>
-      </c>
-      <c r="O9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="12" t="n">
+      <c r="K9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33914</t>
+        </is>
+      </c>
+      <c r="M9" s="12" t="inlineStr">
+        <is>
+          <t>00167633</t>
+        </is>
+      </c>
+      <c r="N9" s="13" t="n">
+        <v>2100</v>
+      </c>
+      <c r="O9" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33755</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MAINTENON] - Migration vers GeoDP V2</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Quentin BORDILLON</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MAINTENON</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G10" s="15" t="inlineStr">
@@ -1449,136 +1458,136 @@
       </c>
       <c r="H10" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I10" s="15" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J10" s="15" t="n">
         <v>1</v>
       </c>
       <c r="K10" s="15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L10" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33764</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M10" s="15" t="inlineStr">
         <is>
-          <t>00169558</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N10" s="16" t="n">
-        <v>1365</v>
-      </c>
-      <c r="O10" s="13" t="n">
-        <v>0</v>
+        <v>657.3</v>
+      </c>
+      <c r="O10" s="17" t="n">
+        <v>219.1</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>0</v>
+        <v>175.28</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-33720</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>[COMMUNE DE LEVALLOIS PERRET] - PRESTA PURGE DES ACTES EN URGENCE</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33804</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>Fabien REUTENAUER</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>PRESTA PURGE DES ACTES EN URGENCE</t>
-        </is>
-      </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>Purge arrêtés temporaires</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="J11" s="11" t="n">
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="J11" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-33724</t>
-        </is>
-      </c>
-      <c r="M11" s="11" t="inlineStr">
-        <is>
-          <t>00169462</t>
-        </is>
-      </c>
-      <c r="N11" s="12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="12" t="n">
+      <c r="K11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33808</t>
+        </is>
+      </c>
+      <c r="M11" s="12" t="inlineStr">
+        <is>
+          <t>00169856</t>
+        </is>
+      </c>
+      <c r="N11" s="13" t="n">
+        <v>1890</v>
+      </c>
+      <c r="O11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33686</t>
+          <t>PDMDEP-33755</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>[EUROMETROPOLE DE METZ] - Paiement CB + 3 PAX</t>
+          <t>[COMMUNE DE MAINTENON] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Quentin BORDILLON</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>EUROMETROPOLE DE METZ</t>
+          <t>COMMUNE DE MAINTENON</t>
         </is>
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>Paiement CB + 3 PAX</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F12" s="15" t="inlineStr">
@@ -1593,12 +1602,12 @@
       </c>
       <c r="H12" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I12" s="15" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J12" s="15" t="n">
@@ -1609,18 +1618,18 @@
       </c>
       <c r="L12" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33694</t>
+          <t>PDMDEP-33764</t>
         </is>
       </c>
       <c r="M12" s="15" t="inlineStr">
         <is>
-          <t>00169321</t>
+          <t>00169558</t>
         </is>
       </c>
       <c r="N12" s="16" t="n">
-        <v>1500</v>
-      </c>
-      <c r="O12" s="13" t="n">
+        <v>1365</v>
+      </c>
+      <c r="O12" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P12" s="16" t="n">
@@ -1628,106 +1637,106 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-33610</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[COMMUNE DE MORLAIX] - MIGRATION GEODP PLACIER hors matériel </t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Quentin BORDILLON</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>COMMUNE DE MORLAIX</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
-        </is>
-      </c>
-      <c r="F13" s="11" t="inlineStr">
-        <is>
-          <t>GEODP</t>
-        </is>
-      </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33720</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>[COMMUNE DE LEVALLOIS PERRET] - PRESTA PURGE DES ACTES EN URGENCE</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>PRESTA PURGE DES ACTES EN URGENCE</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H13" s="11" t="inlineStr">
-        <is>
-          <t>Migration</t>
-        </is>
-      </c>
-      <c r="I13" s="11" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="J13" s="11" t="n">
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J13" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-33616</t>
-        </is>
-      </c>
-      <c r="M13" s="11" t="inlineStr">
-        <is>
-          <t>00169015</t>
-        </is>
-      </c>
-      <c r="N13" s="12" t="n">
-        <v>4040</v>
-      </c>
-      <c r="O13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="12" t="n">
+      <c r="K13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33724</t>
+        </is>
+      </c>
+      <c r="M13" s="12" t="inlineStr">
+        <is>
+          <t>00169462</t>
+        </is>
+      </c>
+      <c r="N13" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O13" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33566</t>
+          <t>PDMDEP-33686</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LILLE] Flux WFS</t>
+          <t>[EUROMETROPOLE DE METZ] - Paiement CB + 3 PAX</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LILLE</t>
+          <t>EUROMETROPOLE DE METZ</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>MM - Up - LiExp - Flux WFS (PS)</t>
+          <t>Paiement CB + 3 PAX</t>
         </is>
       </c>
       <c r="F14" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G14" s="15" t="inlineStr">
@@ -1742,7 +1751,7 @@
       </c>
       <c r="I14" s="15" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="J14" s="15" t="n">
@@ -1753,18 +1762,18 @@
       </c>
       <c r="L14" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33570</t>
+          <t>PDMDEP-33694</t>
         </is>
       </c>
       <c r="M14" s="15" t="inlineStr">
         <is>
-          <t>00168466</t>
+          <t>00169321</t>
         </is>
       </c>
       <c r="N14" s="16" t="n">
-        <v>895</v>
-      </c>
-      <c r="O14" s="13" t="n">
+        <v>1500</v>
+      </c>
+      <c r="O14" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P14" s="16" t="n">
@@ -1772,86 +1781,86 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-33553</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - MM - Up - GeODP - PAX</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Alizée MARGOT</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>MM - Up - GeODP - PAX</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33610</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[COMMUNE DE MORLAIX] - MIGRATION GEODP PLACIER hors matériel </t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Quentin BORDILLON</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE DE MORLAIX</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>GEODP</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="G15" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H15" s="11" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="J15" s="11" t="n">
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="J15" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-33561</t>
-        </is>
-      </c>
-      <c r="M15" s="11" t="inlineStr">
-        <is>
-          <t>00168460</t>
-        </is>
-      </c>
-      <c r="N15" s="12" t="n">
-        <v>500</v>
-      </c>
-      <c r="O15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="12" t="n">
+      <c r="K15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33616</t>
+        </is>
+      </c>
+      <c r="M15" s="12" t="inlineStr">
+        <is>
+          <t>00169015</t>
+        </is>
+      </c>
+      <c r="N15" s="13" t="n">
+        <v>4040</v>
+      </c>
+      <c r="O15" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33566</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t>[COMMUNE DE LILLE] Flux WFS</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -1861,12 +1870,12 @@
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t>COMMUNE DE LILLE</t>
         </is>
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t>MM - Up - LiExp - Flux WFS (PS)</t>
         </is>
       </c>
       <c r="F16" s="15" t="inlineStr">
@@ -1886,29 +1895,29 @@
       </c>
       <c r="I16" s="15" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="J16" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K16" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33570</t>
         </is>
       </c>
       <c r="M16" s="15" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00168466</t>
         </is>
       </c>
       <c r="N16" s="16" t="n">
-        <v>171.4</v>
-      </c>
-      <c r="O16" s="13" t="n">
+        <v>895</v>
+      </c>
+      <c r="O16" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P16" s="16" t="n">
@@ -1916,86 +1925,86 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-33461</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>[Mairie de Buis-les-baronnies] - INITIATION GEODP</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>Maxime PONTONNIER</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>Mairie de Buis-les-baronnies</t>
-        </is>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>INITIATION GEODP</t>
-        </is>
-      </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33553</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - MM - Up - GeODP - PAX</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>MM - Up - GeODP - PAX</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>GEODP</t>
         </is>
       </c>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="G17" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H17" s="11" t="inlineStr">
+      <c r="H17" s="12" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="I17" s="11" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="J17" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-33465</t>
-        </is>
-      </c>
-      <c r="M17" s="11" t="inlineStr">
-        <is>
-          <t>00167986</t>
-        </is>
-      </c>
-      <c r="N17" s="12" t="n">
-        <v>450</v>
-      </c>
-      <c r="O17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" s="12" t="n">
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="J17" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33561</t>
+        </is>
+      </c>
+      <c r="M17" s="12" t="inlineStr">
+        <is>
+          <t>00168460</t>
+        </is>
+      </c>
+      <c r="N17" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="O17" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33386</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
@@ -2005,12 +2014,12 @@
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prestation modélisation Littéralis </t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F18" s="15" t="inlineStr">
@@ -2030,29 +2039,29 @@
       </c>
       <c r="I18" s="15" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J18" s="15" t="n">
         <v>2</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L18" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33390</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M18" s="15" t="inlineStr">
         <is>
-          <t>00167823</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N18" s="16" t="n">
-        <v>205.68</v>
-      </c>
-      <c r="O18" s="13" t="n">
+        <v>171.4</v>
+      </c>
+      <c r="O18" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P18" s="16" t="n">
@@ -2060,101 +2069,101 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-33348</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[MAISONS ALFORT] - Modélisation + Modif Marianne </t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>Fabien REUTENAUER</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">COMMUNE DE MAISONS ALFORT </t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Modélisation + Modif Marianne </t>
-        </is>
-      </c>
-      <c r="F19" s="11" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33461</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>[Mairie de Buis-les-baronnies] - INITIATION GEODP</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Maxime PONTONNIER</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>Mairie de Buis-les-baronnies</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>INITIATION GEODP</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="H19" s="12" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="I19" s="11" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="J19" s="11" t="n">
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="J19" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-33352</t>
-        </is>
-      </c>
-      <c r="M19" s="11" t="inlineStr">
-        <is>
-          <t>00167402</t>
-        </is>
-      </c>
-      <c r="N19" s="12" t="n">
-        <v>171.4</v>
-      </c>
-      <c r="O19" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="12" t="n">
+      <c r="K19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33465</t>
+        </is>
+      </c>
+      <c r="M19" s="12" t="inlineStr">
+        <is>
+          <t>00167986</t>
+        </is>
+      </c>
+      <c r="N19" s="13" t="n">
+        <v>450</v>
+      </c>
+      <c r="O19" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33386</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)</t>
+          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
         </is>
       </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t xml:space="preserve">Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="F20" s="15" t="inlineStr">
@@ -2174,29 +2183,29 @@
       </c>
       <c r="I20" s="15" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J20" s="15" t="n">
         <v>2</v>
       </c>
       <c r="K20" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L20" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33390</t>
         </is>
       </c>
       <c r="M20" s="15" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00167823</t>
         </is>
       </c>
       <c r="N20" s="16" t="n">
-        <v>1250</v>
-      </c>
-      <c r="O20" s="13" t="n">
+        <v>205.68</v>
+      </c>
+      <c r="O20" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P20" s="16" t="n">
@@ -2204,86 +2213,78 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-33227</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>21 crédits d'heure</t>
-        </is>
-      </c>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33363</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>[AMIENS METROPOLE] LiExp - Vérif</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>AMIENS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>MM - Up - LiExp - Vérif</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H21" s="11" t="inlineStr">
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="J21" s="11" t="n">
+      <c r="I21" s="12" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="J21" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-33231</t>
-        </is>
-      </c>
-      <c r="M21" s="11" t="inlineStr">
-        <is>
-          <t>00166707</t>
-        </is>
-      </c>
-      <c r="N21" s="12" t="n">
-        <v>600</v>
+      <c r="K21" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L21" s="12" t="inlineStr"/>
+      <c r="M21" s="12" t="inlineStr"/>
+      <c r="N21" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="O21" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="P21" s="12" t="n">
+      <c r="P21" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33203</t>
+          <t>PDMDEP-33348</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>[CD 38] - LiExp - Crédits d'heure + TDC MV</t>
+          <t xml:space="preserve">[MAISONS ALFORT] - Modélisation + Modif Marianne </t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
@@ -2293,12 +2294,12 @@
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t xml:space="preserve">COMMUNE DE MAISONS ALFORT </t>
         </is>
       </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
-          <t>LiExp - Crédits d'heure + TDC MV</t>
+          <t xml:space="preserve">Modélisation + Modif Marianne </t>
         </is>
       </c>
       <c r="F22" s="15" t="inlineStr">
@@ -2318,7 +2319,7 @@
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="J22" s="15" t="n">
@@ -2329,18 +2330,18 @@
       </c>
       <c r="L22" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33207</t>
+          <t>PDMDEP-33352</t>
         </is>
       </c>
       <c r="M22" s="15" t="inlineStr">
         <is>
-          <t>00166553</t>
+          <t>00167402</t>
         </is>
       </c>
       <c r="N22" s="16" t="n">
-        <v>184.5</v>
-      </c>
-      <c r="O22" s="13" t="n">
+        <v>171.4</v>
+      </c>
+      <c r="O22" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P22" s="16" t="n">
@@ -2348,86 +2349,86 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-33012</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>Alizée MARGOT</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>COMMUNE DE GRASSE</t>
-        </is>
-      </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>Migration GeODP + Module Terrasse + formation sur site</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>GEODP</t>
-        </is>
-      </c>
-      <c r="G23" s="11" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33227</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>21 crédits d'heure</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H23" s="11" t="inlineStr">
-        <is>
-          <t>Migration</t>
-        </is>
-      </c>
-      <c r="I23" s="11" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="J23" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="K23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-33021</t>
-        </is>
-      </c>
-      <c r="M23" s="11" t="inlineStr">
-        <is>
-          <t>00165368</t>
-        </is>
-      </c>
-      <c r="N23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="12" t="n">
-        <v>1079</v>
-      </c>
-      <c r="P23" s="12" t="n">
+      <c r="H23" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I23" s="12" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="J23" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L23" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33232</t>
+        </is>
+      </c>
+      <c r="M23" s="12" t="inlineStr">
+        <is>
+          <t>00166708</t>
+        </is>
+      </c>
+      <c r="N23" s="13" t="n">
+        <v>1250</v>
+      </c>
+      <c r="O23" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
@@ -2437,12 +2438,12 @@
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F24" s="15" t="inlineStr">
@@ -2462,29 +2463,29 @@
       </c>
       <c r="I24" s="15" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J24" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K24" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L24" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M24" s="15" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N24" s="16" t="n">
-        <v>2000</v>
-      </c>
-      <c r="O24" s="13" t="n">
+        <v>600</v>
+      </c>
+      <c r="O24" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P24" s="16" t="n">
@@ -2492,86 +2493,86 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-32848</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>[COMMUNE DE GRENOBLE] - Modification modèles de facture</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>Alizée MARGOT</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>COMMUNE DE GRENOBLE</t>
-        </is>
-      </c>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>Modification modèles de facture</t>
-        </is>
-      </c>
-      <c r="F25" s="11" t="inlineStr">
-        <is>
-          <t>GEODP</t>
-        </is>
-      </c>
-      <c r="G25" s="11" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33203</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>[CD 38] - LiExp - Crédits d'heure + TDC MV</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>LiExp - Crédits d'heure + TDC MV</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H25" s="11" t="inlineStr">
+      <c r="H25" s="12" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="I25" s="11" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="J25" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="K25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-32852</t>
-        </is>
-      </c>
-      <c r="M25" s="11" t="inlineStr">
-        <is>
-          <t>00164564</t>
-        </is>
-      </c>
-      <c r="N25" s="12" t="n">
-        <v>300</v>
-      </c>
-      <c r="O25" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" s="12" t="n">
+      <c r="I25" s="12" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="J25" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33207</t>
+        </is>
+      </c>
+      <c r="M25" s="12" t="inlineStr">
+        <is>
+          <t>00166553</t>
+        </is>
+      </c>
+      <c r="N25" s="13" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="O25" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32831</t>
+          <t>PDMDEP-33012</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE PANTIN] - Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
+          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
@@ -2581,12 +2582,12 @@
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE PANTIN</t>
+          <t>COMMUNE DE GRASSE</t>
         </is>
       </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
-          <t>Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
+          <t>Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="F26" s="15" t="inlineStr">
@@ -2601,141 +2602,141 @@
       </c>
       <c r="H26" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I26" s="15" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J26" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K26" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L26" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32837</t>
+          <t>PDMDEP-33021</t>
         </is>
       </c>
       <c r="M26" s="15" t="inlineStr">
         <is>
-          <t>00164275</t>
+          <t>00165368</t>
         </is>
       </c>
       <c r="N26" s="16" t="n">
-        <v>900</v>
-      </c>
-      <c r="O26" s="13" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O26" s="16" t="n">
+        <v>1079</v>
       </c>
       <c r="P26" s="16" t="n">
-        <v>0</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-32768</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>Fabien REUTENAUER</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="inlineStr">
-        <is>
-          <t>VILLE DE REIMS</t>
-        </is>
-      </c>
-      <c r="E27" s="11" t="inlineStr">
-        <is>
-          <t>MV app/ infra + màj carto</t>
-        </is>
-      </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-32984</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE DE MONTELIMAR</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>Interface Civil net finance avec Littéralis</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="G27" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr">
+      <c r="H27" s="12" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="I27" s="11" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="J27" s="11" t="n">
+      <c r="I27" s="12" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="J27" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-32772</t>
-        </is>
-      </c>
-      <c r="M27" s="11" t="inlineStr">
-        <is>
-          <t>00163806</t>
-        </is>
-      </c>
-      <c r="N27" s="12" t="n">
-        <v>705</v>
-      </c>
-      <c r="O27" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="12" t="n">
+      <c r="K27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-32990</t>
+        </is>
+      </c>
+      <c r="M27" s="12" t="inlineStr">
+        <is>
+          <t>00165270</t>
+        </is>
+      </c>
+      <c r="N27" s="13" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O27" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32759</t>
+          <t>PDMDEP-32848</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE DU GRAND REIMS - DSIT] - MV app/ infra + màj carto</t>
+          <t>[COMMUNE DE GRENOBLE] - Modification modèles de facture</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE DU GRAND REIMS - DSIT</t>
+          <t>COMMUNE DE GRENOBLE</t>
         </is>
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Modification modèles de facture</t>
         </is>
       </c>
       <c r="F28" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G28" s="15" t="inlineStr">
@@ -2750,7 +2751,7 @@
       </c>
       <c r="I28" s="15" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="J28" s="15" t="n">
@@ -2761,18 +2762,18 @@
       </c>
       <c r="L28" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32763</t>
+          <t>PDMDEP-32852</t>
         </is>
       </c>
       <c r="M28" s="15" t="inlineStr">
         <is>
-          <t>00163805</t>
+          <t>00164564</t>
         </is>
       </c>
       <c r="N28" s="16" t="n">
-        <v>564</v>
-      </c>
-      <c r="O28" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="O28" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P28" s="16" t="n">
@@ -2780,106 +2781,106 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-32732</t>
-        </is>
-      </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>Maxime PONTONNIER</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="inlineStr">
-        <is>
-          <t>MAIRIE DE LA SENTINELLE</t>
-        </is>
-      </c>
-      <c r="E29" s="11" t="inlineStr">
-        <is>
-          <t>Acquisition Geodp Caisse</t>
-        </is>
-      </c>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-32831</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>[COMMUNE DE PANTIN] - Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE DE PANTIN</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
         <is>
           <t>GEODP</t>
         </is>
       </c>
-      <c r="G29" s="11" t="inlineStr">
+      <c r="G29" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H29" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
-      <c r="I29" s="11" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="J29" s="11" t="n">
+      <c r="H29" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I29" s="12" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="J29" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K29" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-32741</t>
-        </is>
-      </c>
-      <c r="M29" s="11" t="inlineStr">
-        <is>
-          <t>00163789</t>
-        </is>
-      </c>
-      <c r="N29" s="12" t="n">
-        <v>2138.2</v>
-      </c>
-      <c r="O29" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" s="12" t="n">
+      <c r="K29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-32837</t>
+        </is>
+      </c>
+      <c r="M29" s="12" t="inlineStr">
+        <is>
+          <t>00164275</t>
+        </is>
+      </c>
+      <c r="N29" s="13" t="n">
+        <v>900</v>
+      </c>
+      <c r="O29" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32703</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[MAIRIE DE MIRIBEL] - MIGRATION PLACIER SIMPLE + PAX </t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MIRIBEL</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION PLACIER SIMPLE + PAX </t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F30" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G30" s="15" t="inlineStr">
@@ -2889,12 +2890,12 @@
       </c>
       <c r="H30" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I30" s="15" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J30" s="15" t="n">
@@ -2905,18 +2906,18 @@
       </c>
       <c r="L30" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32712</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M30" s="15" t="inlineStr">
         <is>
-          <t>00163498</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N30" s="16" t="n">
-        <v>283.5</v>
-      </c>
-      <c r="O30" s="13" t="n">
+        <v>705</v>
+      </c>
+      <c r="O30" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P30" s="16" t="n">
@@ -2924,86 +2925,86 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-32625</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="inlineStr">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-32759</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>[COMMUNAUTE URBAINE DU GRAND REIMS - DSIT] - MV app/ infra + màj carto</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
         <is>
           <t>Fabien REUTENAUER</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>COMMUNE D'ANTIBES</t>
-        </is>
-      </c>
-      <c r="E31" s="11" t="inlineStr">
-        <is>
-          <t>Modélisation LiEx</t>
-        </is>
-      </c>
-      <c r="F31" s="11" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNAUTE URBAINE DU GRAND REIMS - DSIT</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>MV app/ infra + màj carto</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="G31" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr">
+      <c r="H31" s="12" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="I31" s="11" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="J31" s="11" t="n">
+      <c r="I31" s="12" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="J31" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K31" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L31" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-32629</t>
-        </is>
-      </c>
-      <c r="M31" s="11" t="inlineStr">
-        <is>
-          <t>00163182</t>
-        </is>
-      </c>
-      <c r="N31" s="12" t="n">
-        <v>548.4</v>
-      </c>
-      <c r="O31" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" s="12" t="n">
+      <c r="K31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-32763</t>
+        </is>
+      </c>
+      <c r="M31" s="12" t="inlineStr">
+        <is>
+          <t>00163805</t>
+        </is>
+      </c>
+      <c r="N31" s="13" t="n">
+        <v>564</v>
+      </c>
+      <c r="O31" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32598</t>
+          <t>PDMDEP-32732</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
+          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
@@ -3013,12 +3014,12 @@
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
+          <t>MAIRIE DE LA SENTINELLE</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>Déploiement GeoDP Caisse</t>
+          <t>Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="F32" s="15" t="inlineStr">
@@ -3038,7 +3039,7 @@
       </c>
       <c r="I32" s="15" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J32" s="15" t="n">
@@ -3049,18 +3050,18 @@
       </c>
       <c r="L32" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32607</t>
+          <t>PDMDEP-32741</t>
         </is>
       </c>
       <c r="M32" s="15" t="inlineStr">
         <is>
-          <t>00163155</t>
+          <t>00163789</t>
         </is>
       </c>
       <c r="N32" s="16" t="n">
-        <v>552</v>
-      </c>
-      <c r="O32" s="13" t="n">
+        <v>2138.2</v>
+      </c>
+      <c r="O32" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P32" s="16" t="n">
@@ -3068,101 +3069,101 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-32461</t>
-        </is>
-      </c>
-      <c r="B33" s="11" t="inlineStr">
-        <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="inlineStr">
-        <is>
-          <t>Alizée MARGOT</t>
-        </is>
-      </c>
-      <c r="D33" s="11" t="inlineStr">
-        <is>
-          <t>NANTES METROPOLE - VDC</t>
-        </is>
-      </c>
-      <c r="E33" s="11" t="inlineStr">
-        <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
-        </is>
-      </c>
-      <c r="F33" s="11" t="inlineStr">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-32703</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[MAIRIE DE MIRIBEL] - MIGRATION PLACIER SIMPLE + PAX </t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>Maxime PONTONNIER</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>MAIRIE DE MIRIBEL</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIGRATION PLACIER SIMPLE + PAX </t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
         <is>
           <t>GEODP</t>
         </is>
       </c>
-      <c r="G33" s="11" t="inlineStr">
+      <c r="G33" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
+      <c r="H33" s="12" t="inlineStr">
         <is>
           <t>Migration</t>
         </is>
       </c>
-      <c r="I33" s="11" t="inlineStr">
-        <is>
-          <t>30/03/2026</t>
-        </is>
-      </c>
-      <c r="J33" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K33" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-32470</t>
-        </is>
-      </c>
-      <c r="M33" s="11" t="inlineStr">
-        <is>
-          <t>00161950</t>
-        </is>
-      </c>
-      <c r="N33" s="12" t="n">
-        <v>1868</v>
-      </c>
-      <c r="O33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" s="12" t="n">
+      <c r="I33" s="12" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="J33" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-32712</t>
+        </is>
+      </c>
+      <c r="M33" s="12" t="inlineStr">
+        <is>
+          <t>00163498</t>
+        </is>
+      </c>
+      <c r="N33" s="13" t="n">
+        <v>283.5</v>
+      </c>
+      <c r="O33" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod </t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E34" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F34" s="15" t="inlineStr">
@@ -3182,29 +3183,29 @@
       </c>
       <c r="I34" s="15" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J34" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K34" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L34" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M34" s="15" t="inlineStr">
         <is>
-          <t>00161842</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N34" s="16" t="n">
-        <v>882.5</v>
-      </c>
-      <c r="O34" s="13" t="n">
+        <v>548.4</v>
+      </c>
+      <c r="O34" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P34" s="16" t="n">
@@ -3212,106 +3213,106 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-32331</t>
-        </is>
-      </c>
-      <c r="B35" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
-        </is>
-      </c>
-      <c r="C35" s="11" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-32598</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
         <is>
           <t>Maxime PONTONNIER</t>
         </is>
       </c>
-      <c r="D35" s="11" t="inlineStr">
-        <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
-        </is>
-      </c>
-      <c r="E35" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
-        </is>
-      </c>
-      <c r="F35" s="11" t="inlineStr">
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement GeoDP Caisse</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
         <is>
           <t>GEODP</t>
         </is>
       </c>
-      <c r="G35" s="11" t="inlineStr">
+      <c r="G35" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H35" s="11" t="inlineStr">
-        <is>
-          <t>Migration</t>
-        </is>
-      </c>
-      <c r="I35" s="11" t="inlineStr">
-        <is>
-          <t>25/03/2026</t>
-        </is>
-      </c>
-      <c r="J35" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-32340</t>
-        </is>
-      </c>
-      <c r="M35" s="11" t="inlineStr">
-        <is>
-          <t>00161493</t>
-        </is>
-      </c>
-      <c r="N35" s="12" t="n">
-        <v>450</v>
-      </c>
-      <c r="O35" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" s="12" t="n">
+      <c r="H35" s="12" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I35" s="12" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="J35" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-32607</t>
+        </is>
+      </c>
+      <c r="M35" s="12" t="inlineStr">
+        <is>
+          <t>00163155</t>
+        </is>
+      </c>
+      <c r="N35" s="13" t="n">
+        <v>552</v>
+      </c>
+      <c r="O35" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E36" s="15" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F36" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G36" s="15" t="inlineStr">
@@ -3321,12 +3322,12 @@
       </c>
       <c r="H36" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I36" s="15" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J36" s="15" t="n">
@@ -3337,18 +3338,18 @@
       </c>
       <c r="L36" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M36" s="15" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N36" s="16" t="n">
-        <v>1046.5</v>
-      </c>
-      <c r="O36" s="13" t="n">
+        <v>1868</v>
+      </c>
+      <c r="O36" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P36" s="16" t="n">
@@ -3356,86 +3357,86 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-32121</t>
-        </is>
-      </c>
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
-        </is>
-      </c>
-      <c r="C37" s="11" t="inlineStr">
-        <is>
-          <t>Alizée MARGOT</t>
-        </is>
-      </c>
-      <c r="D37" s="11" t="inlineStr">
-        <is>
-          <t>COMMUNE DE SARAN</t>
-        </is>
-      </c>
-      <c r="E37" s="11" t="inlineStr">
-        <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
-        </is>
-      </c>
-      <c r="F37" s="11" t="inlineStr">
-        <is>
-          <t>GEODP</t>
-        </is>
-      </c>
-      <c r="G37" s="11" t="inlineStr">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-32442</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod </t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CHAMBERY</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
-        <is>
-          <t>Migration</t>
-        </is>
-      </c>
-      <c r="I37" s="11" t="inlineStr">
-        <is>
-          <t>18/03/2026</t>
-        </is>
-      </c>
-      <c r="J37" s="11" t="n">
+      <c r="H37" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I37" s="12" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="J37" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-32128</t>
-        </is>
-      </c>
-      <c r="M37" s="11" t="inlineStr">
-        <is>
-          <t>00160621</t>
-        </is>
-      </c>
-      <c r="N37" s="12" t="n">
-        <v>250</v>
-      </c>
-      <c r="O37" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" s="12" t="n">
+      <c r="K37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-32446</t>
+        </is>
+      </c>
+      <c r="M37" s="12" t="inlineStr">
+        <is>
+          <t>00161842</t>
+        </is>
+      </c>
+      <c r="N37" s="13" t="n">
+        <v>882.5</v>
+      </c>
+      <c r="O37" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C38" s="15" t="inlineStr">
@@ -3445,12 +3446,12 @@
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E38" s="15" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F38" s="15" t="inlineStr">
@@ -3465,12 +3466,12 @@
       </c>
       <c r="H38" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I38" s="15" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J38" s="15" t="n">
@@ -3481,18 +3482,18 @@
       </c>
       <c r="L38" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M38" s="15" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N38" s="16" t="n">
-        <v>407</v>
-      </c>
-      <c r="O38" s="13" t="n">
+        <v>450</v>
+      </c>
+      <c r="O38" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P38" s="16" t="n">
@@ -3500,101 +3501,101 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-32039</t>
-        </is>
-      </c>
-      <c r="B39" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
-        </is>
-      </c>
-      <c r="C39" s="11" t="inlineStr">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-32264</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
         <is>
           <t>Remy VINCENT</t>
         </is>
       </c>
-      <c r="D39" s="11" t="inlineStr">
-        <is>
-          <t>Commune de la Croix Valmer</t>
-        </is>
-      </c>
-      <c r="E39" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
-        </is>
-      </c>
-      <c r="F39" s="11" t="inlineStr">
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>CA DU NIORTAIS</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>Modélisation</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G39" s="11" t="inlineStr">
+      <c r="G39" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H39" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
-      <c r="I39" s="11" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
-        </is>
-      </c>
-      <c r="J39" s="11" t="n">
+      <c r="H39" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I39" s="12" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J39" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K39" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-32046</t>
-        </is>
-      </c>
-      <c r="M39" s="11" t="inlineStr">
-        <is>
-          <t>00160148</t>
-        </is>
-      </c>
-      <c r="N39" s="12" t="n">
-        <v>440.38</v>
-      </c>
-      <c r="O39" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" s="12" t="n">
+      <c r="K39" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L39" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-32268</t>
+        </is>
+      </c>
+      <c r="M39" s="12" t="inlineStr">
+        <is>
+          <t>00161073</t>
+        </is>
+      </c>
+      <c r="N39" s="13" t="n">
+        <v>1046.5</v>
+      </c>
+      <c r="O39" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E40" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F40" s="15" t="inlineStr">
@@ -3609,12 +3610,12 @@
       </c>
       <c r="H40" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I40" s="15" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J40" s="15" t="n">
@@ -3625,18 +3626,18 @@
       </c>
       <c r="L40" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M40" s="15" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N40" s="16" t="n">
-        <v>285</v>
-      </c>
-      <c r="O40" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="O40" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P40" s="16" t="n">
@@ -3644,86 +3645,86 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-31967</t>
-        </is>
-      </c>
-      <c r="B41" s="11" t="inlineStr">
-        <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
-        </is>
-      </c>
-      <c r="C41" s="11" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
-      <c r="D41" s="11" t="inlineStr">
-        <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
-        </is>
-      </c>
-      <c r="E41" s="11" t="inlineStr">
-        <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
-        </is>
-      </c>
-      <c r="F41" s="11" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G41" s="11" t="inlineStr">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-32086</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>Maxime PONTONNIER</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
+        <is>
+          <t>Acquisition Geodp Placier</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H41" s="11" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
-      <c r="I41" s="11" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="J41" s="11" t="n">
+      <c r="H41" s="12" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I41" s="12" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="J41" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K41" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-31971</t>
-        </is>
-      </c>
-      <c r="M41" s="11" t="inlineStr">
-        <is>
-          <t>00159863</t>
-        </is>
-      </c>
-      <c r="N41" s="12" t="n">
-        <v>2650</v>
-      </c>
-      <c r="O41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" s="12" t="n">
+      <c r="K41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-32095</t>
+        </is>
+      </c>
+      <c r="M41" s="12" t="inlineStr">
+        <is>
+          <t>00160474</t>
+        </is>
+      </c>
+      <c r="N41" s="13" t="n">
+        <v>407</v>
+      </c>
+      <c r="O41" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
@@ -3733,12 +3734,12 @@
       </c>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E42" s="15" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F42" s="15" t="inlineStr">
@@ -3753,12 +3754,12 @@
       </c>
       <c r="H42" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I42" s="15" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J42" s="15" t="n">
@@ -3769,18 +3770,18 @@
       </c>
       <c r="L42" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M42" s="15" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N42" s="16" t="n">
-        <v>120</v>
-      </c>
-      <c r="O42" s="13" t="n">
+        <v>440.38</v>
+      </c>
+      <c r="O42" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P42" s="16" t="n">
@@ -3788,106 +3789,106 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-31649</t>
-        </is>
-      </c>
-      <c r="B43" s="11" t="inlineStr">
-        <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
-        </is>
-      </c>
-      <c r="C43" s="11" t="inlineStr">
-        <is>
-          <t>Alizée MARGOT</t>
-        </is>
-      </c>
-      <c r="D43" s="11" t="inlineStr">
-        <is>
-          <t>MAIRIE DE GUILLESTRE</t>
-        </is>
-      </c>
-      <c r="E43" s="11" t="inlineStr">
-        <is>
-          <t>GeoDP Placier</t>
-        </is>
-      </c>
-      <c r="F43" s="11" t="inlineStr">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-31996</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>Maxime PONTONNIER</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>Commune de Cluny</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="inlineStr">
         <is>
           <t>GEODP</t>
         </is>
       </c>
-      <c r="G43" s="11" t="inlineStr">
+      <c r="G43" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H43" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
-      <c r="I43" s="11" t="inlineStr">
-        <is>
-          <t>27/02/2026</t>
-        </is>
-      </c>
-      <c r="J43" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="K43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-31658</t>
-        </is>
-      </c>
-      <c r="M43" s="11" t="inlineStr">
-        <is>
-          <t>00158175</t>
-        </is>
-      </c>
-      <c r="N43" s="12" t="n">
-        <v>203.5</v>
-      </c>
-      <c r="O43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" s="12" t="n">
+      <c r="H43" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I43" s="12" t="inlineStr">
+        <is>
+          <t>12/03/2026</t>
+        </is>
+      </c>
+      <c r="J43" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-32002</t>
+        </is>
+      </c>
+      <c r="M43" s="12" t="inlineStr">
+        <is>
+          <t>00160078</t>
+        </is>
+      </c>
+      <c r="N43" s="13" t="n">
+        <v>285</v>
+      </c>
+      <c r="O43" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C44" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E44" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F44" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G44" s="15" t="inlineStr">
@@ -3897,34 +3898,34 @@
       </c>
       <c r="H44" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I44" s="15" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J44" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K44" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M44" s="15" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N44" s="16" t="n">
-        <v>150</v>
-      </c>
-      <c r="O44" s="13" t="n">
+        <v>2650</v>
+      </c>
+      <c r="O44" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P44" s="16" t="n">
@@ -3932,106 +3933,106 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-31540</t>
-        </is>
-      </c>
-      <c r="B45" s="11" t="inlineStr">
-        <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
-        </is>
-      </c>
-      <c r="C45" s="11" t="inlineStr">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-31947</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
         <is>
           <t>Remy VINCENT</t>
         </is>
       </c>
-      <c r="D45" s="11" t="inlineStr">
-        <is>
-          <t>COMMUNE DE MONTELIMAR</t>
-        </is>
-      </c>
-      <c r="E45" s="11" t="inlineStr">
-        <is>
-          <t>Modélisation LiEx</t>
-        </is>
-      </c>
-      <c r="F45" s="11" t="inlineStr">
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>SSO/LDAP</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G45" s="11" t="inlineStr">
+      <c r="G45" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H45" s="11" t="inlineStr">
+      <c r="H45" s="12" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="I45" s="11" t="inlineStr">
-        <is>
-          <t>24/02/2026</t>
-        </is>
-      </c>
-      <c r="J45" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="K45" s="11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L45" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-31546</t>
-        </is>
-      </c>
-      <c r="M45" s="11" t="inlineStr">
-        <is>
-          <t>00157816</t>
-        </is>
-      </c>
-      <c r="N45" s="12" t="n">
-        <v>3288.55</v>
-      </c>
-      <c r="O45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" s="12" t="n">
+      <c r="I45" s="12" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="J45" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-31951</t>
+        </is>
+      </c>
+      <c r="M45" s="12" t="inlineStr">
+        <is>
+          <t>00159724</t>
+        </is>
+      </c>
+      <c r="N45" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="O45" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E46" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F46" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G46" s="15" t="inlineStr">
@@ -4041,34 +4042,34 @@
       </c>
       <c r="H46" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I46" s="15" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J46" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K46" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L46" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31468</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M46" s="15" t="inlineStr">
         <is>
-          <t>00157346</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N46" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" s="16" t="n">
+        <v>203.5</v>
+      </c>
+      <c r="O46" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P46" s="16" t="n">
@@ -4076,101 +4077,101 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-31351</t>
-        </is>
-      </c>
-      <c r="B47" s="11" t="inlineStr">
-        <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
-        </is>
-      </c>
-      <c r="C47" s="11" t="inlineStr">
-        <is>
-          <t>Maxime PONTONNIER</t>
-        </is>
-      </c>
-      <c r="D47" s="11" t="inlineStr">
-        <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
-        </is>
-      </c>
-      <c r="E47" s="11" t="inlineStr">
-        <is>
-          <t>Migration vers GeoDP V2</t>
-        </is>
-      </c>
-      <c r="F47" s="11" t="inlineStr">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-31589</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="inlineStr">
         <is>
           <t>GEODP</t>
         </is>
       </c>
-      <c r="G47" s="11" t="inlineStr">
+      <c r="G47" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H47" s="11" t="inlineStr">
+      <c r="H47" s="12" t="inlineStr">
         <is>
           <t>Migration</t>
         </is>
       </c>
-      <c r="I47" s="11" t="inlineStr">
-        <is>
-          <t>17/02/2026</t>
-        </is>
-      </c>
-      <c r="J47" s="11" t="n">
+      <c r="I47" s="12" t="inlineStr">
+        <is>
+          <t>26/02/2026</t>
+        </is>
+      </c>
+      <c r="J47" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K47" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-31360</t>
-        </is>
-      </c>
-      <c r="M47" s="11" t="inlineStr">
-        <is>
-          <t>00157041</t>
-        </is>
-      </c>
-      <c r="N47" s="12" t="n">
-        <v>210</v>
-      </c>
-      <c r="O47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" s="12" t="n">
+      <c r="K47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-31596</t>
+        </is>
+      </c>
+      <c r="M47" s="12" t="inlineStr">
+        <is>
+          <t>00157967</t>
+        </is>
+      </c>
+      <c r="N47" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="O47" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31285</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LUNEL] - FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>Valentin CAUJOLLE</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LUNEL</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E48" s="15" t="inlineStr">
         <is>
-          <t>FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F48" s="15" t="inlineStr">
@@ -4190,29 +4191,29 @@
       </c>
       <c r="I48" s="15" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J48" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K48" s="15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L48" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31289</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M48" s="15" t="inlineStr">
         <is>
-          <t>00156834</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N48" s="16" t="n">
-        <v>71.2</v>
-      </c>
-      <c r="O48" s="13" t="n">
+        <v>3288.55</v>
+      </c>
+      <c r="O48" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P48" s="16" t="n">
@@ -4220,86 +4221,86 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-31188</t>
-        </is>
-      </c>
-      <c r="B49" s="11" t="inlineStr">
-        <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
-        </is>
-      </c>
-      <c r="C49" s="11" t="inlineStr">
-        <is>
-          <t>Maxime PONTONNIER</t>
-        </is>
-      </c>
-      <c r="D49" s="11" t="inlineStr">
-        <is>
-          <t>COMMUNE D HENDAYE</t>
-        </is>
-      </c>
-      <c r="E49" s="11" t="inlineStr">
-        <is>
-          <t>Migration 1 activité GEODP2</t>
-        </is>
-      </c>
-      <c r="F49" s="11" t="inlineStr">
-        <is>
-          <t>GEODP</t>
-        </is>
-      </c>
-      <c r="G49" s="11" t="inlineStr">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-31464</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G49" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H49" s="11" t="inlineStr">
-        <is>
-          <t>Migration</t>
-        </is>
-      </c>
-      <c r="I49" s="11" t="inlineStr">
-        <is>
-          <t>12/02/2026</t>
-        </is>
-      </c>
-      <c r="J49" s="11" t="n">
+      <c r="H49" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I49" s="12" t="inlineStr">
+        <is>
+          <t>19/02/2026</t>
+        </is>
+      </c>
+      <c r="J49" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K49" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-31197</t>
-        </is>
-      </c>
-      <c r="M49" s="11" t="inlineStr">
-        <is>
-          <t>00156556</t>
-        </is>
-      </c>
-      <c r="N49" s="12" t="n">
-        <v>130</v>
+      <c r="K49" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L49" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-31468</t>
+        </is>
+      </c>
+      <c r="M49" s="12" t="inlineStr">
+        <is>
+          <t>00157346</t>
+        </is>
+      </c>
+      <c r="N49" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="O49" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="P49" s="12" t="n">
+      <c r="P49" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C50" s="15" t="inlineStr">
@@ -4309,12 +4310,12 @@
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F50" s="15" t="inlineStr">
@@ -4334,7 +4335,7 @@
       </c>
       <c r="I50" s="15" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J50" s="15" t="n">
@@ -4345,18 +4346,18 @@
       </c>
       <c r="L50" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M50" s="15" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N50" s="16" t="n">
-        <v>255</v>
-      </c>
-      <c r="O50" s="13" t="n">
+        <v>210</v>
+      </c>
+      <c r="O50" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P50" s="16" t="n">
@@ -4364,86 +4365,86 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-30358</t>
-        </is>
-      </c>
-      <c r="B51" s="11" t="inlineStr">
-        <is>
-          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
-        </is>
-      </c>
-      <c r="C51" s="11" t="inlineStr">
-        <is>
-          <t>Maxime PONTONNIER</t>
-        </is>
-      </c>
-      <c r="D51" s="11" t="inlineStr">
-        <is>
-          <t>COMMUNE D'ARGELES-SUR-MER</t>
-        </is>
-      </c>
-      <c r="E51" s="11" t="inlineStr">
-        <is>
-          <t>Migration V2 classique</t>
-        </is>
-      </c>
-      <c r="F51" s="11" t="inlineStr">
-        <is>
-          <t>GEODP</t>
-        </is>
-      </c>
-      <c r="G51" s="11" t="inlineStr">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-31285</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>[COMMUNE DE LUNEL] - FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>Valentin CAUJOLLE</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE DE LUNEL</t>
+        </is>
+      </c>
+      <c r="E51" s="12" t="inlineStr">
+        <is>
+          <t>FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G51" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H51" s="11" t="inlineStr">
-        <is>
-          <t>Migration</t>
-        </is>
-      </c>
-      <c r="I51" s="11" t="inlineStr">
-        <is>
-          <t>29/01/2026</t>
-        </is>
-      </c>
-      <c r="J51" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="K51" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-30366</t>
-        </is>
-      </c>
-      <c r="M51" s="11" t="inlineStr">
-        <is>
-          <t>00154569</t>
-        </is>
-      </c>
-      <c r="N51" s="12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O51" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" s="12" t="n">
+      <c r="H51" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I51" s="12" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J51" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-31289</t>
+        </is>
+      </c>
+      <c r="M51" s="12" t="inlineStr">
+        <is>
+          <t>00156834</t>
+        </is>
+      </c>
+      <c r="N51" s="13" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="O51" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C52" s="15" t="inlineStr">
@@ -4453,7 +4454,7 @@
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E52" s="15" t="inlineStr">
@@ -4478,29 +4479,29 @@
       </c>
       <c r="I52" s="15" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J52" s="15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K52" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M52" s="15" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N52" s="16" t="n">
-        <v>140</v>
-      </c>
-      <c r="O52" s="13" t="n">
+        <v>130</v>
+      </c>
+      <c r="O52" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P52" s="16" t="n">
@@ -4508,106 +4509,106 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-30311</t>
-        </is>
-      </c>
-      <c r="B53" s="11" t="inlineStr">
-        <is>
-          <t>[COMMUNE DE CAEN] - GeODP - Modification des marges via activation Editique</t>
-        </is>
-      </c>
-      <c r="C53" s="11" t="inlineStr">
-        <is>
-          <t>Alizée MARGOT</t>
-        </is>
-      </c>
-      <c r="D53" s="11" t="inlineStr">
-        <is>
-          <t>COMMUNE DE CAEN</t>
-        </is>
-      </c>
-      <c r="E53" s="11" t="inlineStr">
-        <is>
-          <t>GeODP - Modification des marges via activation Editique</t>
-        </is>
-      </c>
-      <c r="F53" s="11" t="inlineStr">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-31036</t>
+        </is>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>Maxime PONTONNIER</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
+        </is>
+      </c>
+      <c r="E53" s="12" t="inlineStr">
+        <is>
+          <t>Migration V2 classique + abo CB</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="inlineStr">
         <is>
           <t>GEODP</t>
         </is>
       </c>
-      <c r="G53" s="11" t="inlineStr">
+      <c r="G53" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H53" s="11" t="inlineStr">
+      <c r="H53" s="12" t="inlineStr">
         <is>
           <t>Migration</t>
         </is>
       </c>
-      <c r="I53" s="11" t="inlineStr">
-        <is>
-          <t>27/01/2026</t>
-        </is>
-      </c>
-      <c r="J53" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="K53" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-30316</t>
-        </is>
-      </c>
-      <c r="M53" s="11" t="inlineStr">
-        <is>
-          <t>00154362</t>
-        </is>
-      </c>
-      <c r="N53" s="12" t="n">
-        <v>200</v>
-      </c>
-      <c r="O53" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" s="12" t="n">
+      <c r="I53" s="12" t="inlineStr">
+        <is>
+          <t>10/02/2026</t>
+        </is>
+      </c>
+      <c r="J53" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-31045</t>
+        </is>
+      </c>
+      <c r="M53" s="12" t="inlineStr">
+        <is>
+          <t>00156095</t>
+        </is>
+      </c>
+      <c r="N53" s="13" t="n">
+        <v>255</v>
+      </c>
+      <c r="O53" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30062</t>
+          <t>PDMDEP-30358</t>
         </is>
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
+          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C54" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
-          <t>Commune de Saint-Dizier</t>
+          <t>COMMUNE D'ARGELES-SUR-MER</t>
         </is>
       </c>
       <c r="E54" s="15" t="inlineStr">
         <is>
-          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F54" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G54" s="15" t="inlineStr">
@@ -4617,12 +4618,12 @@
       </c>
       <c r="H54" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I54" s="15" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="J54" s="15" t="n">
@@ -4633,18 +4634,18 @@
       </c>
       <c r="L54" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30063</t>
+          <t>PDMDEP-30366</t>
         </is>
       </c>
       <c r="M54" s="15" t="inlineStr">
         <is>
-          <t>00153633</t>
+          <t>00154569</t>
         </is>
       </c>
       <c r="N54" s="16" t="n">
-        <v>350</v>
-      </c>
-      <c r="O54" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O54" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P54" s="16" t="n">
@@ -4652,106 +4653,106 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-29948</t>
-        </is>
-      </c>
-      <c r="B55" s="11" t="inlineStr">
-        <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
-        </is>
-      </c>
-      <c r="C55" s="11" t="inlineStr">
-        <is>
-          <t>Fabien REUTENAUER</t>
-        </is>
-      </c>
-      <c r="D55" s="11" t="inlineStr">
-        <is>
-          <t>MAIRE DE PONTARLIER</t>
-        </is>
-      </c>
-      <c r="E55" s="11" t="inlineStr">
-        <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
-        </is>
-      </c>
-      <c r="F55" s="11" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G55" s="11" t="inlineStr">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-30330</t>
+        </is>
+      </c>
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>Maxime PONTONNIER</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE DE ALENCON</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t>Migration 1 activité GEODP2</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="G55" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H55" s="11" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
-      <c r="I55" s="11" t="inlineStr">
-        <is>
-          <t>14/01/2026</t>
-        </is>
-      </c>
-      <c r="J55" s="11" t="n">
+      <c r="H55" s="12" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="I55" s="12" t="inlineStr">
+        <is>
+          <t>28/01/2026</t>
+        </is>
+      </c>
+      <c r="J55" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K55" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L55" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-29949</t>
-        </is>
-      </c>
-      <c r="M55" s="11" t="inlineStr">
-        <is>
-          <t>00152726</t>
-        </is>
-      </c>
-      <c r="N55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="12" t="n">
+      <c r="K55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-30335</t>
+        </is>
+      </c>
+      <c r="M55" s="12" t="inlineStr">
+        <is>
+          <t>00154411</t>
+        </is>
+      </c>
+      <c r="N55" s="13" t="n">
+        <v>140</v>
+      </c>
+      <c r="O55" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30311</t>
         </is>
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[COMMUNE DE CAEN] - GeODP - Modification des marges via activation Editique</t>
         </is>
       </c>
       <c r="C56" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNE DE CAEN</t>
         </is>
       </c>
       <c r="E56" s="15" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>GeODP - Modification des marges via activation Editique</t>
         </is>
       </c>
       <c r="F56" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G56" s="15" t="inlineStr">
@@ -4761,34 +4762,34 @@
       </c>
       <c r="H56" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I56" s="15" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="J56" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K56" s="15" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="L56" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-30316</t>
         </is>
       </c>
       <c r="M56" s="15" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00154362</t>
         </is>
       </c>
       <c r="N56" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="16" t="n">
+        <v>200</v>
+      </c>
+      <c r="O56" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P56" s="16" t="n">
@@ -4796,101 +4797,101 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-29606</t>
-        </is>
-      </c>
-      <c r="B57" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
-        </is>
-      </c>
-      <c r="C57" s="11" t="inlineStr">
-        <is>
-          <t>Fabien REUTENAUER</t>
-        </is>
-      </c>
-      <c r="D57" s="11" t="inlineStr">
-        <is>
-          <t>COMMUNE DE BIARRITZ</t>
-        </is>
-      </c>
-      <c r="E57" s="11" t="inlineStr">
-        <is>
-          <t>Paramétrages complémentaires + Vision</t>
-        </is>
-      </c>
-      <c r="F57" s="11" t="inlineStr">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-30196</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>CD56</t>
+        </is>
+      </c>
+      <c r="E57" s="12" t="inlineStr">
+        <is>
+          <t>Paramétrage interface Pastell</t>
+        </is>
+      </c>
+      <c r="F57" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G57" s="11" t="inlineStr">
+      <c r="G57" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H57" s="11" t="inlineStr">
+      <c r="H57" s="12" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="I57" s="11" t="inlineStr">
-        <is>
-          <t>09/01/2026</t>
-        </is>
-      </c>
-      <c r="J57" s="11" t="n">
+      <c r="I57" s="12" t="inlineStr">
+        <is>
+          <t>21/01/2026</t>
+        </is>
+      </c>
+      <c r="J57" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K57" s="11" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="L57" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-29625</t>
-        </is>
-      </c>
-      <c r="M57" s="11" t="inlineStr">
-        <is>
-          <t>00145091</t>
-        </is>
-      </c>
-      <c r="N57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" s="12" t="n">
+      <c r="K57" s="12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L57" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-30197</t>
+        </is>
+      </c>
+      <c r="M57" s="12" t="inlineStr">
+        <is>
+          <t>00153939</t>
+        </is>
+      </c>
+      <c r="N57" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30062</t>
         </is>
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="C58" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>Commune de Saint-Dizier</t>
         </is>
       </c>
       <c r="E58" s="15" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="F58" s="15" t="inlineStr">
@@ -4910,29 +4911,29 @@
       </c>
       <c r="I58" s="15" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="J58" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K58" s="15" t="n">
-        <v>0.08</v>
+        <v>0.75</v>
       </c>
       <c r="L58" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-30063</t>
         </is>
       </c>
       <c r="M58" s="15" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00153633</t>
         </is>
       </c>
       <c r="N58" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="16" t="n">
+        <v>350</v>
+      </c>
+      <c r="O58" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P58" s="16" t="n">
@@ -4940,98 +4941,102 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-29122</t>
-        </is>
-      </c>
-      <c r="B59" s="11" t="inlineStr">
-        <is>
-          <t>DEPARTEMENT DES DEUX SEVRES (CD 79) - LITTERALIS - Flux WFS communication</t>
-        </is>
-      </c>
-      <c r="C59" s="11" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
-      <c r="D59" s="11" t="inlineStr">
-        <is>
-          <t>DEPARTEMENT DES DEUX SEVRES (CD 79)</t>
-        </is>
-      </c>
-      <c r="E59" s="11" t="n">
-        <v/>
-      </c>
-      <c r="F59" s="11" t="inlineStr">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-29948</t>
+        </is>
+      </c>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>MAIRE DE PONTARLIER</t>
+        </is>
+      </c>
+      <c r="E59" s="12" t="inlineStr">
+        <is>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="F59" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G59" s="11" t="inlineStr">
+      <c r="G59" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H59" s="11" t="inlineStr">
+      <c r="H59" s="12" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="I59" s="11" t="inlineStr">
-        <is>
-          <t>19/12/2025</t>
-        </is>
-      </c>
-      <c r="J59" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="K59" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-29124</t>
-        </is>
-      </c>
-      <c r="M59" s="11" t="inlineStr">
-        <is>
-          <t>00148148</t>
-        </is>
-      </c>
-      <c r="N59" s="12" t="n">
-        <v>157.5</v>
+      <c r="I59" s="12" t="inlineStr">
+        <is>
+          <t>14/01/2026</t>
+        </is>
+      </c>
+      <c r="J59" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K59" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L59" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-29949</t>
+        </is>
+      </c>
+      <c r="M59" s="12" t="inlineStr">
+        <is>
+          <t>00152726</t>
+        </is>
+      </c>
+      <c r="N59" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="P59" s="12" t="n">
+      <c r="P59" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C60" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E60" s="15" t="n">
-        <v/>
+          <t>COMMUNE DE BIARRITZ</t>
+        </is>
+      </c>
+      <c r="E60" s="15" t="inlineStr">
+        <is>
+          <t>Paramétrages complémentaires + Vision</t>
+        </is>
       </c>
       <c r="F60" s="15" t="inlineStr">
         <is>
@@ -5045,34 +5050,34 @@
       </c>
       <c r="H60" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I60" s="15" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J60" s="15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K60" s="15" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="L60" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M60" s="15" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N60" s="16" t="n">
-        <v>2812.32</v>
-      </c>
-      <c r="O60" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P60" s="16" t="n">
@@ -5080,230 +5085,228 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-28095</t>
-        </is>
-      </c>
-      <c r="B61" s="11" t="inlineStr">
-        <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
-        </is>
-      </c>
-      <c r="C61" s="11" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
-      <c r="D61" s="11" t="inlineStr">
-        <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E61" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
-      </c>
-      <c r="F61" s="11" t="inlineStr">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-29606</t>
+        </is>
+      </c>
+      <c r="B61" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+        </is>
+      </c>
+      <c r="C61" s="12" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE DE BIARRITZ</t>
+        </is>
+      </c>
+      <c r="E61" s="12" t="inlineStr">
+        <is>
+          <t>Paramétrages complémentaires + Vision</t>
+        </is>
+      </c>
+      <c r="F61" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G61" s="11" t="inlineStr">
+      <c r="G61" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H61" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
-      <c r="I61" s="11" t="inlineStr">
-        <is>
-          <t>24/11/2025</t>
-        </is>
-      </c>
-      <c r="J61" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K61" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28206</t>
-        </is>
-      </c>
-      <c r="M61" s="11" t="inlineStr">
-        <is>
-          <t>00144864</t>
-        </is>
-      </c>
-      <c r="N61" s="12" t="n">
-        <v>392.5</v>
+      <c r="H61" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I61" s="12" t="inlineStr">
+        <is>
+          <t>09/01/2026</t>
+        </is>
+      </c>
+      <c r="J61" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K61" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="L61" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-29625</t>
+        </is>
+      </c>
+      <c r="M61" s="12" t="inlineStr">
+        <is>
+          <t>00145091</t>
+        </is>
+      </c>
+      <c r="N61" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="O61" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="P61" s="12" t="n">
+      <c r="P61" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C62" s="15" t="inlineStr">
         <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D62" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE DE BIARRITZ</t>
+        </is>
+      </c>
+      <c r="E62" s="15" t="inlineStr">
+        <is>
+          <t>Paramétrages complémentaires + Vision</t>
+        </is>
+      </c>
+      <c r="F62" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G62" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H62" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I62" s="15" t="inlineStr">
+        <is>
+          <t>09/01/2026</t>
+        </is>
+      </c>
+      <c r="J62" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="K62" s="15" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="L62" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-29608</t>
+        </is>
+      </c>
+      <c r="M62" s="15" t="inlineStr">
+        <is>
+          <t>00152338</t>
+        </is>
+      </c>
+      <c r="N62" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-29122</t>
+        </is>
+      </c>
+      <c r="B63" s="12" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DES DEUX SEVRES (CD 79) - LITTERALIS - Flux WFS communication</t>
+        </is>
+      </c>
+      <c r="C63" s="12" t="inlineStr">
+        <is>
           <t>Remy VINCENT</t>
         </is>
       </c>
-      <c r="D62" s="15" t="inlineStr">
-        <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E62" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
-      </c>
-      <c r="F62" s="15" t="inlineStr">
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DES DEUX SEVRES (CD 79)</t>
+        </is>
+      </c>
+      <c r="E63" s="12" t="n">
+        <v/>
+      </c>
+      <c r="F63" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G62" s="15" t="inlineStr">
+      <c r="G63" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H62" s="15" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
-      <c r="I62" s="15" t="inlineStr">
-        <is>
-          <t>24/11/2025</t>
-        </is>
-      </c>
-      <c r="J62" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="K62" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28205</t>
-        </is>
-      </c>
-      <c r="M62" s="15" t="inlineStr">
-        <is>
-          <t>00144863</t>
-        </is>
-      </c>
-      <c r="N62" s="16" t="n">
-        <v>1556.25</v>
-      </c>
-      <c r="O62" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" s="16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-28095</t>
-        </is>
-      </c>
-      <c r="B63" s="11" t="inlineStr">
-        <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
-        </is>
-      </c>
-      <c r="C63" s="11" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
-      <c r="D63" s="11" t="inlineStr">
-        <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E63" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
-      </c>
-      <c r="F63" s="11" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G63" s="11" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H63" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
-      <c r="I63" s="11" t="inlineStr">
-        <is>
-          <t>24/11/2025</t>
-        </is>
-      </c>
-      <c r="J63" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K63" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28204</t>
-        </is>
-      </c>
-      <c r="M63" s="11" t="inlineStr">
-        <is>
-          <t>00144862</t>
-        </is>
-      </c>
-      <c r="N63" s="12" t="n">
-        <v>1790</v>
-      </c>
-      <c r="O63" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" s="12" t="n">
+      <c r="H63" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I63" s="12" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="J63" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K63" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-29124</t>
+        </is>
+      </c>
+      <c r="M63" s="12" t="inlineStr">
+        <is>
+          <t>00148148</t>
+        </is>
+      </c>
+      <c r="N63" s="13" t="n">
+        <v>157.5</v>
+      </c>
+      <c r="O63" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
@@ -5313,7 +5316,7 @@
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
+          <t>COMMUNE DE BOBIGNY</t>
         </is>
       </c>
       <c r="E64" s="15" t="n">
@@ -5336,7 +5339,7 @@
       </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J64" s="15" t="n">
@@ -5347,18 +5350,18 @@
       </c>
       <c r="L64" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M64" s="15" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N64" s="16" t="n">
-        <v>732</v>
-      </c>
-      <c r="O64" s="13" t="n">
+        <v>2812.32</v>
+      </c>
+      <c r="O64" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P64" s="16" t="n">
@@ -5366,86 +5369,86 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-26782</t>
-        </is>
-      </c>
-      <c r="B65" s="11" t="inlineStr">
-        <is>
-          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
-        </is>
-      </c>
-      <c r="C65" s="11" t="inlineStr">
-        <is>
-          <t>Fabien REUTENAUER</t>
-        </is>
-      </c>
-      <c r="D65" s="11" t="inlineStr">
-        <is>
-          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
-        </is>
-      </c>
-      <c r="E65" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement LiEx</t>
-        </is>
-      </c>
-      <c r="F65" s="11" t="inlineStr">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28095</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E65" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="F65" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G65" s="11" t="inlineStr">
+      <c r="G65" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H65" s="11" t="inlineStr">
+      <c r="H65" s="12" t="inlineStr">
         <is>
           <t>Nouveau déploiement</t>
         </is>
       </c>
-      <c r="I65" s="11" t="inlineStr">
-        <is>
-          <t>03/11/2025</t>
-        </is>
-      </c>
-      <c r="J65" s="11" t="n">
+      <c r="I65" s="12" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J65" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="K65" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L65" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-26783</t>
-        </is>
-      </c>
-      <c r="M65" s="11" t="inlineStr">
-        <is>
-          <t>00142659</t>
-        </is>
-      </c>
-      <c r="N65" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" s="12" t="n">
+      <c r="K65" s="12" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L65" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28206</t>
+        </is>
+      </c>
+      <c r="M65" s="12" t="inlineStr">
+        <is>
+          <t>00144864</t>
+        </is>
+      </c>
+      <c r="N65" s="13" t="n">
+        <v>392.5</v>
+      </c>
+      <c r="O65" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
@@ -5455,11 +5458,13 @@
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
-        </is>
-      </c>
-      <c r="E66" s="15" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E66" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F66" s="15" t="inlineStr">
         <is>
@@ -5478,29 +5483,29 @@
       </c>
       <c r="I66" s="15" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J66" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K66" s="15" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="L66" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M66" s="15" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N66" s="16" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O66" s="13" t="n">
+        <v>1556.25</v>
+      </c>
+      <c r="O66" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P66" s="16" t="n">
@@ -5508,84 +5513,86 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-24426</t>
-        </is>
-      </c>
-      <c r="B67" s="11" t="inlineStr">
-        <is>
-          <t>[DRANCY] - Migration STD vers Exp</t>
-        </is>
-      </c>
-      <c r="C67" s="11" t="inlineStr">
-        <is>
-          <t>Fabien REUTENAUER</t>
-        </is>
-      </c>
-      <c r="D67" s="11" t="inlineStr">
-        <is>
-          <t>VILLE DE DRANCY</t>
-        </is>
-      </c>
-      <c r="E67" s="11" t="n">
-        <v/>
-      </c>
-      <c r="F67" s="11" t="inlineStr">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28095</t>
+        </is>
+      </c>
+      <c r="B67" s="12" t="inlineStr">
+        <is>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="C67" s="12" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E67" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="F67" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G67" s="11" t="inlineStr">
+      <c r="G67" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H67" s="11" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
-      <c r="I67" s="11" t="inlineStr">
-        <is>
-          <t>30/09/2025</t>
-        </is>
-      </c>
-      <c r="J67" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="K67" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L67" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27028</t>
-        </is>
-      </c>
-      <c r="M67" s="11" t="inlineStr">
-        <is>
-          <t>500950</t>
-        </is>
-      </c>
-      <c r="N67" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O67" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" s="12" t="n">
+      <c r="H67" s="12" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I67" s="12" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J67" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K67" s="12" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L67" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28204</t>
+        </is>
+      </c>
+      <c r="M67" s="12" t="inlineStr">
+        <is>
+          <t>00144862</t>
+        </is>
+      </c>
+      <c r="N67" s="13" t="n">
+        <v>1790</v>
+      </c>
+      <c r="O67" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
@@ -5595,11 +5602,13 @@
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
-        </is>
-      </c>
-      <c r="E68" s="15" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E68" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F68" s="15" t="inlineStr">
         <is>
@@ -5618,29 +5627,29 @@
       </c>
       <c r="I68" s="15" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J68" s="15" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K68" s="15" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="L68" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M68" s="15" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N68" s="16" t="n">
-        <v>2323</v>
-      </c>
-      <c r="O68" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P68" s="16" t="n">
@@ -5648,94 +5657,96 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-23484</t>
-        </is>
-      </c>
-      <c r="B69" s="11" t="inlineStr">
-        <is>
-          <t>METROPOLE TOULON- AJOUT LIEU DE NAISSANCE DANS FILIEN</t>
-        </is>
-      </c>
-      <c r="C69" s="11" t="inlineStr">
-        <is>
-          <t>Alizée MARGOT</t>
-        </is>
-      </c>
-      <c r="D69" s="11" t="inlineStr">
-        <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
-        </is>
-      </c>
-      <c r="E69" s="11" t="n">
-        <v/>
-      </c>
-      <c r="F69" s="11" t="inlineStr">
-        <is>
-          <t>GEODP</t>
-        </is>
-      </c>
-      <c r="G69" s="11" t="inlineStr">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28095</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="inlineStr">
+        <is>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="C69" s="12" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="F69" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G69" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H69" s="11" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
-      <c r="I69" s="11" t="inlineStr">
-        <is>
-          <t>25/07/2025</t>
-        </is>
-      </c>
-      <c r="J69" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="K69" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27494</t>
-        </is>
-      </c>
-      <c r="M69" s="11" t="inlineStr">
-        <is>
-          <t>495695</t>
-        </is>
-      </c>
-      <c r="N69" s="12" t="n">
-        <v>140.4</v>
+      <c r="H69" s="12" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I69" s="12" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J69" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K69" s="12" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L69" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28202</t>
+        </is>
+      </c>
+      <c r="M69" s="12" t="inlineStr">
+        <is>
+          <t>00144857</t>
+        </is>
+      </c>
+      <c r="N69" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="O69" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="P69" s="12" t="n">
+      <c r="P69" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22996</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
         </is>
       </c>
       <c r="E70" s="15" t="n">
@@ -5758,23 +5769,23 @@
       </c>
       <c r="I70" s="15" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J70" s="15" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K70" s="15" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="L70" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28051</t>
+          <t>PDMDEP-27642</t>
         </is>
       </c>
       <c r="M70" s="15" t="inlineStr">
         <is>
-          <t>487190</t>
+          <t>00143935</t>
         </is>
       </c>
       <c r="N70" s="16" t="n">
@@ -5788,224 +5799,226 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-21546</t>
-        </is>
-      </c>
-      <c r="B71" s="11" t="inlineStr">
-        <is>
-          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
-        </is>
-      </c>
-      <c r="C71" s="11" t="inlineStr">
-        <is>
-          <t>Alizée MARGOT</t>
-        </is>
-      </c>
-      <c r="D71" s="11" t="inlineStr">
-        <is>
-          <t>VILLEURBANNE</t>
-        </is>
-      </c>
-      <c r="E71" s="11" t="n">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27543</t>
+        </is>
+      </c>
+      <c r="B71" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="C71" s="12" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
+        </is>
+      </c>
+      <c r="E71" s="12" t="n">
         <v/>
       </c>
-      <c r="F71" s="11" t="inlineStr">
-        <is>
-          <t>GEODP</t>
-        </is>
-      </c>
-      <c r="G71" s="11" t="inlineStr">
+      <c r="F71" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G71" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H71" s="11" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
-      <c r="I71" s="11" t="inlineStr">
-        <is>
-          <t>05/05/2025</t>
-        </is>
-      </c>
-      <c r="J71" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="K71" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28038</t>
-        </is>
-      </c>
-      <c r="M71" s="11" t="inlineStr">
-        <is>
-          <t>478867</t>
-        </is>
-      </c>
-      <c r="N71" s="12" t="n">
-        <v>1413.6</v>
-      </c>
-      <c r="O71" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" s="12" t="n">
+      <c r="H71" s="12" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I71" s="12" t="inlineStr">
+        <is>
+          <t>20/11/2025</t>
+        </is>
+      </c>
+      <c r="J71" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K71" s="12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L71" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27557</t>
+        </is>
+      </c>
+      <c r="M71" s="12" t="inlineStr">
+        <is>
+          <t>00144532</t>
+        </is>
+      </c>
+      <c r="N71" s="13" t="n">
+        <v>732</v>
+      </c>
+      <c r="O71" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-26782</t>
         </is>
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D72" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
+        </is>
+      </c>
+      <c r="E72" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement LiEx</t>
+        </is>
+      </c>
+      <c r="F72" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G72" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H72" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I72" s="15" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="J72" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="K72" s="15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L72" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-26783</t>
+        </is>
+      </c>
+      <c r="M72" s="15" t="inlineStr">
+        <is>
+          <t>00142659</t>
+        </is>
+      </c>
+      <c r="N72" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-24866</t>
+        </is>
+      </c>
+      <c r="B73" s="12" t="inlineStr">
+        <is>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="C73" s="12" t="inlineStr">
+        <is>
           <t>Remy VINCENT</t>
         </is>
       </c>
-      <c r="D72" s="15" t="inlineStr">
-        <is>
-          <t>MONTREUIL</t>
-        </is>
-      </c>
-      <c r="E72" s="15" t="n">
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="n">
         <v/>
       </c>
-      <c r="F72" s="15" t="inlineStr">
+      <c r="F73" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G72" s="15" t="inlineStr">
+      <c r="G73" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H72" s="15" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
-      <c r="I72" s="15" t="inlineStr">
-        <is>
-          <t>18/04/2025</t>
-        </is>
-      </c>
-      <c r="J72" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="K72" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28035</t>
-        </is>
-      </c>
-      <c r="M72" s="15" t="inlineStr">
-        <is>
-          <t>468660</t>
-        </is>
-      </c>
-      <c r="N72" s="16" t="n">
-        <v>250</v>
-      </c>
-      <c r="O72" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" s="16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-20907</t>
-        </is>
-      </c>
-      <c r="B73" s="11" t="inlineStr">
-        <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
-        </is>
-      </c>
-      <c r="C73" s="11" t="inlineStr">
-        <is>
-          <t>Fabien REUTENAUER</t>
-        </is>
-      </c>
-      <c r="D73" s="11" t="inlineStr">
-        <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
-        </is>
-      </c>
-      <c r="E73" s="11" t="n">
-        <v/>
-      </c>
-      <c r="F73" s="11" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G73" s="11" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H73" s="11" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
-      <c r="I73" s="11" t="inlineStr">
-        <is>
-          <t>14/04/2025</t>
-        </is>
-      </c>
-      <c r="J73" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="K73" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28034</t>
-        </is>
-      </c>
-      <c r="M73" s="11" t="inlineStr">
-        <is>
-          <t>475575</t>
-        </is>
-      </c>
-      <c r="N73" s="12" t="n">
-        <v>460</v>
-      </c>
-      <c r="O73" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" s="12" t="n">
+      <c r="H73" s="12" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I73" s="12" t="inlineStr">
+        <is>
+          <t>16/10/2025</t>
+        </is>
+      </c>
+      <c r="J73" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K73" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27017</t>
+        </is>
+      </c>
+      <c r="M73" s="12" t="inlineStr">
+        <is>
+          <t>00141205</t>
+        </is>
+      </c>
+      <c r="N73" s="13" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O73" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
@@ -6015,7 +6028,7 @@
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>VILLE DE DRANCY</t>
         </is>
       </c>
       <c r="E74" s="15" t="n">
@@ -6033,28 +6046,28 @@
       </c>
       <c r="H74" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I74" s="15" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J74" s="15" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K74" s="15" t="n">
         <v>0.25</v>
       </c>
       <c r="L74" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-27028</t>
         </is>
       </c>
       <c r="M74" s="15" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="N74" s="16" t="n">
@@ -6068,84 +6081,84 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-19385</t>
-        </is>
-      </c>
-      <c r="B75" s="11" t="inlineStr">
-        <is>
-          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
-        </is>
-      </c>
-      <c r="C75" s="11" t="inlineStr">
-        <is>
-          <t>Fabien REUTENAUER</t>
-        </is>
-      </c>
-      <c r="D75" s="11" t="inlineStr">
-        <is>
-          <t>COMMUNE D'ARCUEIL</t>
-        </is>
-      </c>
-      <c r="E75" s="11" t="n">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-23918</t>
+        </is>
+      </c>
+      <c r="B75" s="12" t="inlineStr">
+        <is>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="C75" s="12" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+        </is>
+      </c>
+      <c r="E75" s="12" t="n">
         <v/>
       </c>
-      <c r="F75" s="11" t="inlineStr">
+      <c r="F75" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G75" s="11" t="inlineStr">
+      <c r="G75" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H75" s="11" t="inlineStr">
+      <c r="H75" s="12" t="inlineStr">
         <is>
           <t>Nouveau déploiement</t>
         </is>
       </c>
-      <c r="I75" s="11" t="inlineStr">
-        <is>
-          <t>24/02/2025</t>
-        </is>
-      </c>
-      <c r="J75" s="11" t="n">
-        <v>17</v>
-      </c>
-      <c r="K75" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L75" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27535</t>
-        </is>
-      </c>
-      <c r="M75" s="11" t="inlineStr">
-        <is>
-          <t>465345</t>
-        </is>
-      </c>
-      <c r="N75" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" s="12" t="n">
+      <c r="I75" s="12" t="inlineStr">
+        <is>
+          <t>26/08/2025</t>
+        </is>
+      </c>
+      <c r="J75" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="K75" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28055</t>
+        </is>
+      </c>
+      <c r="M75" s="12" t="inlineStr">
+        <is>
+          <t>499132</t>
+        </is>
+      </c>
+      <c r="N75" s="13" t="n">
+        <v>2323</v>
+      </c>
+      <c r="O75" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-23484</t>
         </is>
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>METROPOLE TOULON- AJOUT LIEU DE NAISSANCE DANS FILIEN</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
@@ -6155,7 +6168,7 @@
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E76" s="15" t="n">
@@ -6173,34 +6186,34 @@
       </c>
       <c r="H76" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>25/07/2025</t>
         </is>
       </c>
       <c r="J76" s="15" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="K76" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L76" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-27494</t>
         </is>
       </c>
       <c r="M76" s="15" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>495695</t>
         </is>
       </c>
       <c r="N76" s="16" t="n">
-        <v>240</v>
-      </c>
-      <c r="O76" s="13" t="n">
+        <v>140.4</v>
+      </c>
+      <c r="O76" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P76" s="16" t="n">
@@ -6208,84 +6221,84 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-18038</t>
-        </is>
-      </c>
-      <c r="B77" s="11" t="inlineStr">
-        <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
-        </is>
-      </c>
-      <c r="C77" s="11" t="inlineStr">
+      <c r="A77" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-22996</t>
+        </is>
+      </c>
+      <c r="B77" s="12" t="inlineStr">
+        <is>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="C77" s="12" t="inlineStr">
         <is>
           <t>Fabien REUTENAUER</t>
         </is>
       </c>
-      <c r="D77" s="11" t="inlineStr">
-        <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
-        </is>
-      </c>
-      <c r="E77" s="11" t="n">
+      <c r="D77" s="12" t="inlineStr">
+        <is>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+        </is>
+      </c>
+      <c r="E77" s="12" t="n">
         <v/>
       </c>
-      <c r="F77" s="11" t="inlineStr">
+      <c r="F77" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G77" s="11" t="inlineStr">
+      <c r="G77" s="12" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H77" s="11" t="inlineStr">
+      <c r="H77" s="12" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="I77" s="11" t="inlineStr">
-        <is>
-          <t>12/12/2024</t>
-        </is>
-      </c>
-      <c r="J77" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="K77" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L77" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28020</t>
-        </is>
-      </c>
-      <c r="M77" s="11" t="inlineStr">
-        <is>
-          <t>458057</t>
-        </is>
-      </c>
-      <c r="N77" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P77" s="12" t="n">
+      <c r="I77" s="12" t="inlineStr">
+        <is>
+          <t>07/07/2025</t>
+        </is>
+      </c>
+      <c r="J77" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="K77" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L77" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28051</t>
+        </is>
+      </c>
+      <c r="M77" s="12" t="inlineStr">
+        <is>
+          <t>487190</t>
+        </is>
+      </c>
+      <c r="N77" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-16868</t>
+          <t>PDMDEP-21546</t>
         </is>
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>[Limoges] migration placier</t>
+          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
@@ -6295,7 +6308,7 @@
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>Limoges</t>
+          <t>VILLEURBANNE</t>
         </is>
       </c>
       <c r="E78" s="15" t="n">
@@ -6308,31 +6321,39 @@
       </c>
       <c r="G78" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H78" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
-          <t>26/09/2024</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="J78" s="15" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="K78" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L78" s="15" t="inlineStr"/>
-      <c r="M78" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L78" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28038</t>
+        </is>
+      </c>
+      <c r="M78" s="15" t="inlineStr">
+        <is>
+          <t>478867</t>
+        </is>
+      </c>
       <c r="N78" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" s="16" t="n">
+        <v>1413.6</v>
+      </c>
+      <c r="O78" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P78" s="16" t="n">
@@ -6340,76 +6361,84 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="10" t="inlineStr">
-        <is>
-          <t>PDMDEP-14551</t>
-        </is>
-      </c>
-      <c r="B79" s="11" t="inlineStr">
-        <is>
-          <t>[Perpignan] Interface formulaire</t>
-        </is>
-      </c>
-      <c r="C79" s="11" t="inlineStr">
-        <is>
-          <t>Fabien REUTENAUER</t>
-        </is>
-      </c>
-      <c r="D79" s="11" t="inlineStr">
-        <is>
-          <t>[Perpignan]</t>
-        </is>
-      </c>
-      <c r="E79" s="11" t="n">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-21165</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="inlineStr">
+        <is>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+        </is>
+      </c>
+      <c r="C79" s="12" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D79" s="12" t="inlineStr">
+        <is>
+          <t>MONTREUIL</t>
+        </is>
+      </c>
+      <c r="E79" s="12" t="n">
         <v/>
       </c>
-      <c r="F79" s="11" t="inlineStr">
+      <c r="F79" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G79" s="11" t="inlineStr">
-        <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H79" s="11" t="inlineStr">
+      <c r="G79" s="12" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H79" s="12" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="I79" s="11" t="inlineStr">
-        <is>
-          <t>14/03/2024</t>
-        </is>
-      </c>
-      <c r="J79" s="11" t="n">
-        <v>28</v>
-      </c>
-      <c r="K79" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L79" s="11" t="inlineStr"/>
-      <c r="M79" s="11" t="inlineStr"/>
-      <c r="N79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" s="12" t="n">
+      <c r="I79" s="12" t="inlineStr">
+        <is>
+          <t>18/04/2025</t>
+        </is>
+      </c>
+      <c r="J79" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="K79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28035</t>
+        </is>
+      </c>
+      <c r="M79" s="12" t="inlineStr">
+        <is>
+          <t>468660</t>
+        </is>
+      </c>
+      <c r="N79" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="O79" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
@@ -6419,13 +6448,11 @@
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E80" s="15" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>SAINT PIERRE (LA REUNION)</t>
+        </is>
+      </c>
+      <c r="E80" s="15" t="n">
+        <v/>
       </c>
       <c r="F80" s="15" t="inlineStr">
         <is>
@@ -6434,7 +6461,7 @@
       </c>
       <c r="G80" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H80" s="15" t="inlineStr">
@@ -6444,173 +6471,709 @@
       </c>
       <c r="I80" s="15" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J80" s="15" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="K80" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L80" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M80" s="15" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
+      <c r="N80" s="16" t="n">
+        <v>460</v>
+      </c>
+      <c r="O80" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-19792</t>
+        </is>
+      </c>
+      <c r="B81" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+        </is>
+      </c>
+      <c r="C81" s="12" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D81" s="12" t="inlineStr">
+        <is>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+        </is>
+      </c>
+      <c r="E81" s="12" t="n">
+        <v/>
+      </c>
+      <c r="F81" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G81" s="12" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H81" s="12" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I81" s="12" t="inlineStr">
+        <is>
+          <t>06/03/2025</t>
+        </is>
+      </c>
+      <c r="J81" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="K81" s="12" t="n">
         <v>0.25</v>
       </c>
-      <c r="L80" s="15" t="inlineStr"/>
-      <c r="M80" s="15" t="inlineStr"/>
-      <c r="N80" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" s="16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="10" t="inlineStr">
-        <is>
-          <t>PSC-1270</t>
-        </is>
-      </c>
-      <c r="B81" s="11" t="inlineStr">
-        <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="C81" s="11" t="inlineStr"/>
-      <c r="D81" s="11" t="inlineStr">
-        <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="E81" s="11" t="inlineStr"/>
-      <c r="F81" s="11" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G81" s="11" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H81" s="11" t="inlineStr"/>
-      <c r="I81" s="11" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="J81" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K81" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M81" s="11" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
-      <c r="N81" s="12" t="n">
-        <v>510.6</v>
+      <c r="L81" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27377</t>
+        </is>
+      </c>
+      <c r="M81" s="12" t="inlineStr">
+        <is>
+          <t>478048</t>
+        </is>
+      </c>
+      <c r="N81" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="O81" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="P81" s="12" t="n">
+      <c r="P81" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
+          <t>PDMDEP-19385</t>
+        </is>
+      </c>
+      <c r="B82" s="15" t="inlineStr">
+        <is>
+          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
+        </is>
+      </c>
+      <c r="C82" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D82" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE D'ARCUEIL</t>
+        </is>
+      </c>
+      <c r="E82" s="15" t="n">
+        <v/>
+      </c>
+      <c r="F82" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G82" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H82" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I82" s="15" t="inlineStr">
+        <is>
+          <t>24/02/2025</t>
+        </is>
+      </c>
+      <c r="J82" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="K82" s="15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L82" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27535</t>
+        </is>
+      </c>
+      <c r="M82" s="15" t="inlineStr">
+        <is>
+          <t>465345</t>
+        </is>
+      </c>
+      <c r="N82" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-18115</t>
+        </is>
+      </c>
+      <c r="B83" s="12" t="inlineStr">
+        <is>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
+        </is>
+      </c>
+      <c r="C83" s="12" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="D83" s="12" t="inlineStr">
+        <is>
+          <t>BISCHWILLER</t>
+        </is>
+      </c>
+      <c r="E83" s="12" t="n">
+        <v/>
+      </c>
+      <c r="F83" s="12" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="G83" s="12" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H83" s="12" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="I83" s="12" t="inlineStr">
+        <is>
+          <t>17/12/2024</t>
+        </is>
+      </c>
+      <c r="J83" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="K83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M83" s="12" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
+      <c r="N83" s="13" t="n">
+        <v>240</v>
+      </c>
+      <c r="O83" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-18038</t>
+        </is>
+      </c>
+      <c r="B84" s="15" t="inlineStr">
+        <is>
+          <t>[CD 38] Reprise de 1644 AP</t>
+        </is>
+      </c>
+      <c r="C84" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D84" s="15" t="inlineStr">
+        <is>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+        </is>
+      </c>
+      <c r="E84" s="15" t="n">
+        <v/>
+      </c>
+      <c r="F84" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G84" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H84" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I84" s="15" t="inlineStr">
+        <is>
+          <t>12/12/2024</t>
+        </is>
+      </c>
+      <c r="J84" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="K84" s="15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L84" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28020</t>
+        </is>
+      </c>
+      <c r="M84" s="15" t="inlineStr">
+        <is>
+          <t>458057</t>
+        </is>
+      </c>
+      <c r="N84" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-16868</t>
+        </is>
+      </c>
+      <c r="B85" s="12" t="inlineStr">
+        <is>
+          <t>[Limoges] migration placier</t>
+        </is>
+      </c>
+      <c r="C85" s="12" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="D85" s="12" t="inlineStr">
+        <is>
+          <t>Limoges</t>
+        </is>
+      </c>
+      <c r="E85" s="12" t="n">
+        <v/>
+      </c>
+      <c r="F85" s="12" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="G85" s="12" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H85" s="12" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="I85" s="12" t="inlineStr">
+        <is>
+          <t>26/09/2024</t>
+        </is>
+      </c>
+      <c r="J85" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="K85" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L85" s="12" t="inlineStr"/>
+      <c r="M85" s="12" t="inlineStr"/>
+      <c r="N85" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-14551</t>
+        </is>
+      </c>
+      <c r="B86" s="15" t="inlineStr">
+        <is>
+          <t>[Perpignan] Interface formulaire</t>
+        </is>
+      </c>
+      <c r="C86" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D86" s="15" t="inlineStr">
+        <is>
+          <t>[Perpignan]</t>
+        </is>
+      </c>
+      <c r="E86" s="15" t="n">
+        <v/>
+      </c>
+      <c r="F86" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G86" s="15" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H86" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I86" s="15" t="inlineStr">
+        <is>
+          <t>14/03/2024</t>
+        </is>
+      </c>
+      <c r="J86" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="K86" s="15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L86" s="15" t="inlineStr"/>
+      <c r="M86" s="15" t="inlineStr"/>
+      <c r="N86" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-12222</t>
+        </is>
+      </c>
+      <c r="B87" s="12" t="inlineStr">
+        <is>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C87" s="12" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>CD14</t>
+        </is>
+      </c>
+      <c r="E87" s="12" t="inlineStr">
+        <is>
+          <t>Modélisation spécifique</t>
+        </is>
+      </c>
+      <c r="F87" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G87" s="12" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H87" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I87" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2023</t>
+        </is>
+      </c>
+      <c r="J87" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="K87" s="12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L87" s="12" t="inlineStr"/>
+      <c r="M87" s="12" t="inlineStr"/>
+      <c r="N87" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-11477</t>
+        </is>
+      </c>
+      <c r="B88" s="15" t="inlineStr">
+        <is>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C88" s="15" t="inlineStr"/>
+      <c r="D88" s="15" t="inlineStr">
+        <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E88" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
+      <c r="F88" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G88" s="15" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H88" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I88" s="15" t="inlineStr">
+        <is>
+          <t>03/09/2023</t>
+        </is>
+      </c>
+      <c r="J88" s="15" t="n">
+        <v>34</v>
+      </c>
+      <c r="K88" s="15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L88" s="15" t="inlineStr"/>
+      <c r="M88" s="15" t="inlineStr"/>
+      <c r="N88" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="11" t="inlineStr">
+        <is>
+          <t>PSC-1270</t>
+        </is>
+      </c>
+      <c r="B89" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="C89" s="12" t="inlineStr"/>
+      <c r="D89" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="E89" s="12" t="inlineStr"/>
+      <c r="F89" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G89" s="12" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H89" s="12" t="inlineStr"/>
+      <c r="I89" s="12" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J89" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M89" s="12" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N89" s="13" t="n">
+        <v>510.6</v>
+      </c>
+      <c r="O89" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="14" t="inlineStr">
+        <is>
           <t>PSC-1228</t>
         </is>
       </c>
-      <c r="B82" s="15" t="inlineStr">
+      <c r="B90" s="15" t="inlineStr">
         <is>
           <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
-      <c r="C82" s="15" t="inlineStr"/>
-      <c r="D82" s="15" t="inlineStr">
+      <c r="C90" s="15" t="inlineStr"/>
+      <c r="D90" s="15" t="inlineStr">
         <is>
           <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
-      <c r="E82" s="15" t="inlineStr"/>
-      <c r="F82" s="15" t="inlineStr">
+      <c r="E90" s="15" t="inlineStr"/>
+      <c r="F90" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G82" s="15" t="inlineStr">
+      <c r="G90" s="15" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H82" s="15" t="inlineStr"/>
-      <c r="I82" s="15" t="inlineStr">
+      <c r="H90" s="15" t="inlineStr"/>
+      <c r="I90" s="15" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="J82" s="15" t="n">
+      <c r="J90" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="K82" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="15" t="inlineStr">
+      <c r="K90" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="15" t="inlineStr">
         <is>
           <t>PDMDEP-32829</t>
         </is>
       </c>
-      <c r="M82" s="15" t="inlineStr">
+      <c r="M90" s="15" t="inlineStr">
         <is>
           <t>00163534</t>
         </is>
       </c>
-      <c r="N82" s="16" t="n">
+      <c r="N90" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="O82" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" s="16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="17" t="inlineStr">
+      <c r="O90" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B83" s="17" t="inlineStr"/>
-      <c r="C83" s="17" t="inlineStr"/>
-      <c r="D83" s="17" t="inlineStr"/>
-      <c r="E83" s="17" t="inlineStr"/>
-      <c r="F83" s="17" t="inlineStr"/>
-      <c r="G83" s="17" t="inlineStr"/>
-      <c r="H83" s="17" t="inlineStr"/>
-      <c r="I83" s="17" t="inlineStr"/>
-      <c r="J83" s="17" t="inlineStr"/>
-      <c r="K83" s="17" t="inlineStr"/>
-      <c r="L83" s="17" t="inlineStr"/>
-      <c r="M83" s="17" t="inlineStr"/>
-      <c r="N83" s="18" t="n">
+      <c r="B91" s="18" t="inlineStr"/>
+      <c r="C91" s="18" t="inlineStr"/>
+      <c r="D91" s="18" t="inlineStr"/>
+      <c r="E91" s="18" t="inlineStr"/>
+      <c r="F91" s="18" t="inlineStr"/>
+      <c r="G91" s="18" t="inlineStr"/>
+      <c r="H91" s="18" t="inlineStr"/>
+      <c r="I91" s="18" t="inlineStr"/>
+      <c r="J91" s="18" t="inlineStr"/>
+      <c r="K91" s="18" t="inlineStr"/>
+      <c r="L91" s="18" t="inlineStr"/>
+      <c r="M91" s="18" t="inlineStr"/>
+      <c r="N91" s="19" t="n">
         <v>56751.68</v>
       </c>
-      <c r="O83" s="18" t="n">
+      <c r="O91" s="19" t="n">
         <v>1298.1</v>
       </c>
-      <c r="P83" s="18" t="n">
-        <v>144.39</v>
+      <c r="P91" s="19" t="n">
+        <v>44.39</v>
       </c>
     </row>
   </sheetData>
@@ -6694,6 +7257,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6737,57 +7308,57 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Epic Nom</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>Solution</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>Type de deal</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>Temps mois (h)</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="10" t="inlineStr">
         <is>
           <t>Ticket CA</t>
         </is>
       </c>
-      <c r="J4" s="9" t="inlineStr">
+      <c r="J4" s="10" t="inlineStr">
         <is>
           <t>Numéro BDC</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="10" t="inlineStr">
         <is>
           <t>Montant déclaré ce mois</t>
         </is>
@@ -6829,24 +7400,24 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Indicateur</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Valeur</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Effectif de l'équipe</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>8 personnes</t>
         </is>
@@ -6865,12 +7436,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Jours ouvrés du mois</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>22</t>
         </is>
@@ -6889,12 +7460,12 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Capacité totale disponible</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>879 h</t>
         </is>
@@ -6902,41 +7473,41 @@
     </row>
     <row r="10"/>
     <row r="11">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>Répartition théorique — Littéralis (CD)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>% théorique</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>Heures théoriques</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Productif</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="C13" s="11" t="n">
+      <c r="C13" s="12" t="n">
         <v>278.25</v>
       </c>
     </row>
@@ -6956,57 +7527,57 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Interne</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="C15" s="11" t="n">
+      <c r="C15" s="12" t="n">
         <v>18.55</v>
       </c>
     </row>
     <row r="16"/>
     <row r="17">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>Répartition théorique — GEODP (CD)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="21" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="B18" s="20" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>% théorique</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>Heures théoriques</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>Productif</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="C19" s="11" t="n">
+      <c r="C19" s="12" t="n">
         <v>263.34</v>
       </c>
     </row>
@@ -7026,57 +7597,57 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>Interne</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="C21" s="11" t="n">
+      <c r="C21" s="12" t="n">
         <v>13.86</v>
       </c>
     </row>
     <row r="22"/>
     <row r="23">
-      <c r="A23" s="19" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>Répartition théorique — Chefs de projet</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="B24" s="20" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>% théorique</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>Heures théoriques</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>Productif</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="C25" s="11" t="n">
+      <c r="C25" s="12" t="n">
         <v>207.9</v>
       </c>
     </row>
@@ -7096,57 +7667,57 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>Interne</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="C27" s="11" t="n">
+      <c r="C27" s="12" t="n">
         <v>23.1</v>
       </c>
     </row>
     <row r="28"/>
     <row r="29">
-      <c r="A29" s="19" t="inlineStr">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>Répartition théorique — Équipe globale</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="20" t="inlineStr">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="B30" s="20" t="inlineStr">
+      <c r="B30" s="21" t="inlineStr">
         <is>
           <t>% théorique</t>
         </is>
       </c>
-      <c r="C30" s="20" t="inlineStr">
+      <c r="C30" s="21" t="inlineStr">
         <is>
           <t>Heures théoriques</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>Productif</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="C31" s="11" t="n">
+      <c r="C31" s="12" t="n">
         <v>749.49</v>
       </c>
     </row>
@@ -7166,17 +7737,17 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>Interne</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="C33" s="11" t="n">
+      <c r="C33" s="12" t="n">
         <v>55.51</v>
       </c>
     </row>
@@ -7220,42 +7791,42 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Solution</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Projet avec CA</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Rework</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>Gratuit</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>Productif (total)</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>Capacité productive</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>% occupation</t>
         </is>
@@ -7268,68 +7839,68 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>8</v>
+        <v>19.75</v>
       </c>
       <c r="C5" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="D5" s="15" t="n">
-        <v>0</v>
-      </c>
       <c r="E5" s="15" t="n">
-        <v>8.5</v>
+        <v>25.25</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>486.15</v>
       </c>
-      <c r="H5" s="21" t="inlineStr">
-        <is>
-          <t>1.7%</t>
+      <c r="H5" s="22" t="inlineStr">
+        <is>
+          <t>5.2%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>GEODP</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="11" t="n">
+      <c r="B6" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="12" t="n">
         <v>263.34</v>
       </c>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t>0.2%</t>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>1.5%</t>
         </is>
       </c>
     </row>
     <row r="7"/>
     <row r="8">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Interne (toutes équipes)</t>
         </is>
       </c>
-      <c r="B8" s="23" t="n">
-        <v>2.75</v>
+      <c r="B8" s="24" t="n">
+        <v>7.25</v>
       </c>
     </row>
   </sheetData>
@@ -7371,64 +7942,64 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Périmètre</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Backlog total</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Mobilisable</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>dont Blocage client</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>dont Blocage commerce</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>dont Blocage produit</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B5" s="24" t="n">
-        <v>393221</v>
-      </c>
-      <c r="C5" s="24" t="n">
-        <v>191962</v>
-      </c>
-      <c r="D5" s="24" t="n">
+      <c r="B5" s="25" t="n">
+        <v>395260</v>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>194001</v>
+      </c>
+      <c r="D5" s="25" t="n">
         <v>201259</v>
       </c>
-      <c r="E5" s="24" t="n">
+      <c r="E5" s="25" t="n">
         <v>169899</v>
       </c>
-      <c r="F5" s="24" t="n">
+      <c r="F5" s="25" t="n">
         <v>15760</v>
       </c>
-      <c r="G5" s="24" t="n">
+      <c r="G5" s="25" t="n">
         <v>15599</v>
       </c>
     </row>
@@ -7438,47 +8009,47 @@
           <t>Littéralis</t>
         </is>
       </c>
-      <c r="B6" s="25" t="n">
+      <c r="B6" s="26" t="n">
         <v>187891</v>
       </c>
-      <c r="C6" s="25" t="n">
+      <c r="C6" s="26" t="n">
         <v>83887</v>
       </c>
-      <c r="D6" s="25" t="n">
+      <c r="D6" s="26" t="n">
         <v>104005</v>
       </c>
-      <c r="E6" s="25" t="n">
+      <c r="E6" s="26" t="n">
         <v>96496</v>
       </c>
-      <c r="F6" s="25" t="n">
+      <c r="F6" s="26" t="n">
         <v>3060</v>
       </c>
-      <c r="G6" s="25" t="n">
+      <c r="G6" s="26" t="n">
         <v>4448</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>GEODP</t>
         </is>
       </c>
-      <c r="B7" s="26" t="n">
-        <v>205330</v>
-      </c>
-      <c r="C7" s="26" t="n">
-        <v>108075</v>
-      </c>
-      <c r="D7" s="26" t="n">
+      <c r="B7" s="27" t="n">
+        <v>207369</v>
+      </c>
+      <c r="C7" s="27" t="n">
+        <v>110114</v>
+      </c>
+      <c r="D7" s="27" t="n">
         <v>97254</v>
       </c>
-      <c r="E7" s="26" t="n">
+      <c r="E7" s="27" t="n">
         <v>73403</v>
       </c>
-      <c r="F7" s="26" t="n">
+      <c r="F7" s="27" t="n">
         <v>12700</v>
       </c>
-      <c r="G7" s="26" t="n">
+      <c r="G7" s="27" t="n">
         <v>11151</v>
       </c>
     </row>
@@ -7523,47 +8094,47 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Ticket CA</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Date commande</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>Solution</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>Type de deal</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>Prestation</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>Numéro BDC</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="10" t="inlineStr">
         <is>
           <t>Montant (€)</t>
         </is>
@@ -7610,115 +8181,115 @@
           <t>00171793</t>
         </is>
       </c>
-      <c r="I5" s="25" t="n">
+      <c r="I5" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>PDMDEP-34362</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>PDMDEP-34358</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>01/07/2026</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>458057</t>
         </is>
       </c>
-      <c r="I6" s="26" t="n">
+      <c r="I6" s="27" t="n">
         <v>6806.25</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n"/>
-      <c r="C7" s="17" t="n"/>
-      <c r="D7" s="17" t="n"/>
-      <c r="E7" s="17" t="n"/>
-      <c r="F7" s="17" t="n"/>
-      <c r="G7" s="17" t="n"/>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="B7" s="18" t="n"/>
+      <c r="C7" s="18" t="n"/>
+      <c r="D7" s="18" t="n"/>
+      <c r="E7" s="18" t="n"/>
+      <c r="F7" s="18" t="n"/>
+      <c r="G7" s="18" t="n"/>
+      <c r="H7" s="18" t="inlineStr">
         <is>
           <t>2 commande(s)</t>
         </is>
       </c>
-      <c r="I7" s="24" t="n">
+      <c r="I7" s="25" t="n">
         <v>6806</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>dont Littéralis</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n"/>
-      <c r="C8" s="17" t="n"/>
-      <c r="D8" s="17" t="n"/>
-      <c r="E8" s="17" t="n"/>
-      <c r="F8" s="17" t="n"/>
-      <c r="G8" s="17" t="n"/>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="B8" s="18" t="n"/>
+      <c r="C8" s="18" t="n"/>
+      <c r="D8" s="18" t="n"/>
+      <c r="E8" s="18" t="n"/>
+      <c r="F8" s="18" t="n"/>
+      <c r="G8" s="18" t="n"/>
+      <c r="H8" s="18" t="inlineStr">
         <is>
           <t>1 commande(s)</t>
         </is>
       </c>
-      <c r="I8" s="24" t="n">
+      <c r="I8" s="25" t="n">
         <v>6806</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>dont GEODP</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n"/>
-      <c r="C9" s="17" t="n"/>
-      <c r="D9" s="17" t="n"/>
-      <c r="E9" s="17" t="n"/>
-      <c r="F9" s="17" t="n"/>
-      <c r="G9" s="17" t="n"/>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="B9" s="18" t="n"/>
+      <c r="C9" s="18" t="n"/>
+      <c r="D9" s="18" t="n"/>
+      <c r="E9" s="18" t="n"/>
+      <c r="F9" s="18" t="n"/>
+      <c r="G9" s="18" t="n"/>
+      <c r="H9" s="18" t="inlineStr">
         <is>
           <t>1 commande(s)</t>
         </is>
       </c>
-      <c r="I9" s="24" t="n">
+      <c r="I9" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7760,32 +8331,32 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Nom</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>Solution</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>Ancienneté (mois)</t>
         </is>
@@ -7793,30 +8364,30 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>TOTAL projets clôturés</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n"/>
-      <c r="C6" s="17" t="n"/>
-      <c r="D6" s="17" t="n"/>
-      <c r="E6" s="17" t="n"/>
-      <c r="F6" s="17" t="n">
+      <c r="B6" s="18" t="n"/>
+      <c r="C6" s="18" t="n"/>
+      <c r="D6" s="18" t="n"/>
+      <c r="E6" s="18" t="n"/>
+      <c r="F6" s="18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>TOTAL rework clôturés</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27" t="n">
+      <c r="B7" s="28" t="n"/>
+      <c r="C7" s="28" t="n"/>
+      <c r="D7" s="28" t="n"/>
+      <c r="E7" s="28" t="n"/>
+      <c r="F7" s="28" t="n">
         <v>0</v>
       </c>
     </row>
